--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\47213138\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{7D052B84-7E34-4ED8-A436-FE35B0B6D839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14561ACA-DB96-4D8A-BDE1-93394491D890}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="226">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -711,6 +711,9 @@
   </si>
   <si>
     <t>VŠE</t>
+  </si>
+  <si>
+    <t>https://ies.fsv.cuni.cz/en/contacts/institute-members/67299512</t>
   </si>
 </sst>
 </file>
@@ -2218,6 +2221,9 @@
       <c r="F59" t="s">
         <v>183</v>
       </c>
+      <c r="H59" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\47213138\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D33071E-2EB9-44A1-A6A5-3B742C00E632}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="237">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -714,13 +714,46 @@
   </si>
   <si>
     <t>https://ies.fsv.cuni.cz/en/contacts/institute-members/67299512</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>Adam_Geršl.jpg</t>
+  </si>
+  <si>
+    <t>https://ies.fsv.cuni.cz/contacts/institute-members/95375215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman Horvath is Professor at the Institute of Economic Studies, Faculty of Social Sciences, Charles University in Prague. He previously served as Head of the Research Unit and Advisor to the Board at the Czech National Bank, and as President of the Czech Economic Society. His research has been published in leading journals including the Journal of International Economics, IMF Economic Review, Journal of Money, Credit and Banking, Review of Economic Dynamics, World Development, and the World Bank Economic Review, among many others. He is Associate Editor of the Journal of Financial Stability and serves on the Board of Advisors of Open Economies Review. He has also acted as a consultant to several institutions, including the European Parliament, where he was a member of the Monetary Experts Panel, and the World Bank.  </t>
+  </si>
+  <si>
+    <t>https://ies.fsv.cuni.cz/en/contacts/institute-members/59321289</t>
+  </si>
+  <si>
+    <t>Doktorand na Institutu ekonomických studií</t>
+  </si>
+  <si>
+    <t>https://simonamalovana.com/</t>
+  </si>
+  <si>
+    <t>Simona Malovaná is an Assistant Professor at the Institute of Economic Studies, Faculty of Social Sciences, Charles University. She works at the intersection of central banking, financial stability, and macro-financial policy. Her research explores how monetary and macroprudential policies affect credit, banking, and the wider economy, and how climate and geopolitical risks shape financial systems. She also serves as Executive Director of the Research and Statistics Department at the Czech National Bank.</t>
+  </si>
+  <si>
+    <t>Matej_Korinek.jpg</t>
+  </si>
+  <si>
+    <t>Petr_Teply.png</t>
+  </si>
+  <si>
+    <t>Simona_Malovana.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -734,6 +767,15 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -753,14 +795,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="normální 2" xfId="1" xr:uid="{1A109594-AF6E-4195-BD8E-00D2077CAC21}"/>
   </cellStyles>
@@ -1094,13 +1139,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE358DA8-D777-4377-96EA-27F7BC555635}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>130</v>
       </c>
@@ -1125,8 +1170,11 @@
       <c r="H1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -1146,7 +1194,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>147</v>
       </c>
@@ -1166,7 +1214,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>148</v>
       </c>
@@ -1186,7 +1234,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>149</v>
       </c>
@@ -1206,7 +1254,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -1226,7 +1274,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -1246,7 +1294,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -1263,7 +1311,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>153</v>
       </c>
@@ -1283,7 +1331,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>154</v>
       </c>
@@ -1303,7 +1351,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>155</v>
       </c>
@@ -1323,7 +1371,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>156</v>
       </c>
@@ -1343,7 +1391,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>157</v>
       </c>
@@ -1363,7 +1411,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>158</v>
       </c>
@@ -1383,7 +1431,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>159</v>
       </c>
@@ -1403,7 +1451,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>160</v>
       </c>
@@ -1743,7 +1791,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>176</v>
       </c>
@@ -1763,7 +1811,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>177</v>
       </c>
@@ -1783,7 +1831,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>178</v>
       </c>
@@ -1803,7 +1851,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>179</v>
       </c>
@@ -1823,7 +1871,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>180</v>
       </c>
@@ -1840,7 +1888,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>181</v>
       </c>
@@ -1860,7 +1908,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>182</v>
       </c>
@@ -1880,12 +1928,12 @@
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>130</v>
       </c>
@@ -1910,8 +1958,11 @@
       <c r="H42" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -1931,7 +1982,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>186</v>
       </c>
@@ -1951,7 +2002,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>187</v>
       </c>
@@ -1971,7 +2022,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>188</v>
       </c>
@@ -1991,7 +2042,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>189</v>
       </c>
@@ -2011,7 +2062,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>190</v>
       </c>
@@ -2031,7 +2082,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>191</v>
       </c>
@@ -2051,7 +2102,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>192</v>
       </c>
@@ -2071,7 +2122,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>193</v>
       </c>
@@ -2091,7 +2142,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>194</v>
       </c>
@@ -2111,7 +2162,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>195</v>
       </c>
@@ -2131,7 +2182,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>196</v>
       </c>
@@ -2151,12 +2202,12 @@
         <v>183</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>130</v>
       </c>
@@ -2181,8 +2232,11 @@
       <c r="H57" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>197</v>
       </c>
@@ -2202,7 +2256,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>200</v>
       </c>
@@ -2224,8 +2278,11 @@
       <c r="H59" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>201</v>
       </c>
@@ -2244,8 +2301,14 @@
       <c r="F60" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G60" t="s">
+        <v>229</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>202</v>
       </c>
@@ -2265,7 +2328,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>203</v>
       </c>
@@ -2284,8 +2347,17 @@
       <c r="F62" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G62" t="s">
+        <v>233</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I62" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>204</v>
       </c>
@@ -2305,7 +2377,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>205</v>
       </c>
@@ -2324,8 +2396,14 @@
       <c r="F64" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H64" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I64" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>206</v>
       </c>
@@ -2345,7 +2423,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>207</v>
       </c>
@@ -2365,7 +2443,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>208</v>
       </c>
@@ -2385,7 +2463,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>209</v>
       </c>
@@ -2405,7 +2483,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>210</v>
       </c>
@@ -2424,13 +2502,19 @@
       <c r="F69" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G69" t="s">
+        <v>231</v>
+      </c>
+      <c r="I69" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>130</v>
       </c>
@@ -2455,8 +2539,11 @@
       <c r="H72" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I72" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>211</v>
       </c>
@@ -2473,7 +2560,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>213</v>
       </c>
@@ -2493,7 +2580,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>214</v>
       </c>
@@ -2513,7 +2600,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>215</v>
       </c>
@@ -2530,7 +2617,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>216</v>
       </c>
@@ -2550,7 +2637,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>217</v>
       </c>
@@ -2570,7 +2657,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>218</v>
       </c>
@@ -2590,7 +2677,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>219</v>
       </c>
@@ -2631,6 +2718,12 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I59" r:id="rId1" tooltip="Adam_Geršl.jpg" display="https://github.com/kpp-sketch/cios_website/blob/main/public/Adam_Ger%C5%A1l.jpg" xr:uid="{D50D89A4-5891-490B-BEF1-EA3A0BBB4952}"/>
+    <hyperlink ref="H64" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
+    <hyperlink ref="H60" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
+    <hyperlink ref="H62" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D33071E-2EB9-44A1-A6A5-3B742C00E632}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{787986D3-EDD5-4683-8F5F-9CD85396F308}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -380,9 +380,6 @@
     <t>Kořínek</t>
   </si>
   <si>
-    <t>26749713@fsv.cuni.cz</t>
-  </si>
-  <si>
     <t>Bennis</t>
   </si>
   <si>
@@ -731,9 +728,6 @@
     <t>https://ies.fsv.cuni.cz/en/contacts/institute-members/59321289</t>
   </si>
   <si>
-    <t>Doktorand na Institutu ekonomických studií</t>
-  </si>
-  <si>
     <t>https://simonamalovana.com/</t>
   </si>
   <si>
@@ -747,6 +741,12 @@
   </si>
   <si>
     <t>Simona_Malovana.jpg</t>
+  </si>
+  <si>
+    <t>matej.korinek@fsv.cuni.cz</t>
+  </si>
+  <si>
+    <t>Doctoral student at the Institute of Economic Studies</t>
   </si>
 </sst>
 </file>
@@ -1147,1574 +1147,1574 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>131</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>132</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>133</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>134</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>135</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>136</v>
       </c>
-      <c r="H1" t="s">
-        <v>137</v>
-      </c>
       <c r="I1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
         <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
         <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" t="s">
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
         <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
         <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
         <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
         <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
         <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s">
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
         <v>52</v>
       </c>
       <c r="E28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
         <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
         <v>55</v>
       </c>
       <c r="E30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
         <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
         <v>57</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s">
         <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
         <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s">
         <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
         <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B34" t="s">
         <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
         <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B35" t="s">
         <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
         <v>66</v>
       </c>
       <c r="E35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
         <v>67</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
         <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
         <v>69</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B38" t="s">
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
         <v>72</v>
       </c>
       <c r="E38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B39" t="s">
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
         <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" t="s">
         <v>130</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>131</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>132</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>133</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>134</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>135</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>136</v>
       </c>
-      <c r="H42" t="s">
-        <v>137</v>
-      </c>
       <c r="I42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B43" t="s">
         <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
         <v>78</v>
       </c>
       <c r="E43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s">
         <v>79</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
         <v>80</v>
       </c>
       <c r="E44" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B45" t="s">
         <v>81</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" t="s">
         <v>82</v>
       </c>
       <c r="E45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B46" t="s">
         <v>83</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
         <v>84</v>
       </c>
       <c r="E46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B47" t="s">
         <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
         <v>86</v>
       </c>
       <c r="E47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B48" t="s">
         <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
         <v>88</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B49" t="s">
         <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D49" t="s">
         <v>90</v>
       </c>
       <c r="E49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B50" t="s">
         <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
         <v>92</v>
       </c>
       <c r="E50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
         <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D51" t="s">
         <v>94</v>
       </c>
       <c r="E51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" t="s">
         <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
         <v>96</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" t="s">
         <v>97</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D53" t="s">
         <v>98</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" t="s">
         <v>99</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
         <v>100</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" t="s">
         <v>130</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>131</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>132</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>133</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>134</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>135</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>136</v>
       </c>
-      <c r="H57" t="s">
-        <v>137</v>
-      </c>
       <c r="I57" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
+        <v>197</v>
+      </c>
+      <c r="E58" t="s">
         <v>198</v>
       </c>
-      <c r="E58" t="s">
-        <v>199</v>
-      </c>
       <c r="F58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s">
         <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
         <v>101</v>
       </c>
       <c r="E59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F59" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B60" t="s">
         <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
         <v>102</v>
       </c>
       <c r="E60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G60" t="s">
+        <v>228</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
         <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D61" t="s">
         <v>103</v>
       </c>
       <c r="E61" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
         <v>46</v>
       </c>
       <c r="C62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
         <v>104</v>
       </c>
       <c r="E62" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G62" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
         <v>64</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s">
         <v>105</v>
       </c>
       <c r="E63" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
         <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D64" t="s">
         <v>106</v>
       </c>
       <c r="E64" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F64" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I64" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
       </c>
       <c r="C65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65" t="s">
         <v>107</v>
       </c>
       <c r="E65" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B66" t="s">
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
         <v>108</v>
       </c>
       <c r="E66" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B67" t="s">
         <v>109</v>
       </c>
       <c r="C67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D67" t="s">
         <v>110</v>
       </c>
       <c r="E67" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B68" t="s">
         <v>111</v>
       </c>
       <c r="C68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
         <v>112</v>
       </c>
       <c r="E68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B69" t="s">
         <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
-      </c>
-      <c r="D69" t="s">
-        <v>114</v>
+        <v>137</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="E69" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G69" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I69" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
         <v>130</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>131</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>132</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>133</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>134</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>135</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>136</v>
       </c>
-      <c r="H72" t="s">
-        <v>137</v>
-      </c>
       <c r="I72" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>210</v>
+      </c>
+      <c r="B73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" t="s">
+        <v>137</v>
+      </c>
+      <c r="E73" t="s">
         <v>211</v>
       </c>
-      <c r="B73" t="s">
-        <v>115</v>
-      </c>
-      <c r="C73" t="s">
-        <v>138</v>
-      </c>
-      <c r="E73" t="s">
-        <v>212</v>
-      </c>
       <c r="F73" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B74" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D74" t="s">
         <v>116</v>
       </c>
-      <c r="C74" t="s">
-        <v>138</v>
-      </c>
-      <c r="D74" t="s">
-        <v>117</v>
-      </c>
       <c r="E74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B75" t="s">
+        <v>117</v>
+      </c>
+      <c r="C75" t="s">
+        <v>137</v>
+      </c>
+      <c r="D75" t="s">
         <v>118</v>
       </c>
-      <c r="C75" t="s">
-        <v>138</v>
-      </c>
-      <c r="D75" t="s">
-        <v>119</v>
-      </c>
       <c r="E75" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E76" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F76" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B77" t="s">
         <v>73</v>
       </c>
       <c r="C77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E77" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B78" t="s">
+        <v>121</v>
+      </c>
+      <c r="C78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D78" t="s">
         <v>122</v>
       </c>
-      <c r="C78" t="s">
-        <v>138</v>
-      </c>
-      <c r="D78" t="s">
-        <v>123</v>
-      </c>
       <c r="E78" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F78" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B79" t="s">
+        <v>123</v>
+      </c>
+      <c r="C79" t="s">
+        <v>137</v>
+      </c>
+      <c r="D79" t="s">
         <v>124</v>
       </c>
-      <c r="C79" t="s">
-        <v>138</v>
-      </c>
-      <c r="D79" t="s">
-        <v>125</v>
-      </c>
       <c r="E79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B80" t="s">
+        <v>125</v>
+      </c>
+      <c r="C80" t="s">
+        <v>137</v>
+      </c>
+      <c r="D80" t="s">
         <v>126</v>
       </c>
-      <c r="C80" t="s">
-        <v>138</v>
-      </c>
-      <c r="D80" t="s">
-        <v>127</v>
-      </c>
       <c r="E80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B81" t="s">
+        <v>127</v>
+      </c>
+      <c r="C81" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81" t="s">
         <v>128</v>
       </c>
-      <c r="C81" t="s">
-        <v>138</v>
-      </c>
-      <c r="D81" t="s">
-        <v>129</v>
-      </c>
       <c r="E81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F81" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2723,6 +2723,7 @@
     <hyperlink ref="H64" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
     <hyperlink ref="H60" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
     <hyperlink ref="H62" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
+    <hyperlink ref="D69" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{787986D3-EDD5-4683-8F5F-9CD85396F308}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D9E0D1C-761F-4DE7-A1B6-EDB74DAFDC44}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="238">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -747,6 +747,9 @@
   </si>
   <si>
     <t>Doctoral student at the Institute of Economic Studies</t>
+  </si>
+  <si>
+    <t>Roman_Horváth.jpg</t>
   </si>
 </sst>
 </file>
@@ -2307,6 +2310,9 @@
       <c r="H60" s="1" t="s">
         <v>229</v>
       </c>
+      <c r="I60" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D9E0D1C-761F-4DE7-A1B6-EDB74DAFDC44}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB046E4A-9BF9-49CD-AE96-9B8590ADBAF3}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -134,9 +134,6 @@
     <t>Jelínek</t>
   </si>
   <si>
-    <t>jelinekf@prf.cuni.cz</t>
-  </si>
-  <si>
     <t>Kabasakal Badamchi</t>
   </si>
   <si>
@@ -750,6 +747,9 @@
   </si>
   <si>
     <t>Roman_Horváth.jpg</t>
+  </si>
+  <si>
+    <t>fjelinek@prf.cuni.cz</t>
   </si>
 </sst>
 </file>
@@ -1150,1577 +1150,1577 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" t="s">
         <v>129</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>130</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>131</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>132</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>133</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>134</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>135</v>
       </c>
-      <c r="H1" t="s">
-        <v>136</v>
-      </c>
       <c r="I1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
+        <v>136</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" t="s">
-        <v>137</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" t="s">
         <v>35</v>
       </c>
-      <c r="C20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D20" t="s">
-        <v>36</v>
-      </c>
       <c r="E20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" t="s">
-        <v>38</v>
-      </c>
       <c r="E21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" t="s">
         <v>39</v>
       </c>
-      <c r="C22" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" t="s">
-        <v>40</v>
-      </c>
       <c r="E22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" t="s">
         <v>41</v>
       </c>
-      <c r="C23" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" t="s">
-        <v>42</v>
-      </c>
       <c r="E23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" t="s">
         <v>43</v>
       </c>
-      <c r="C24" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" t="s">
-        <v>44</v>
-      </c>
       <c r="E24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
         <v>47</v>
       </c>
-      <c r="C26" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" t="s">
-        <v>48</v>
-      </c>
       <c r="E26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" t="s">
         <v>49</v>
       </c>
-      <c r="C27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" t="s">
-        <v>50</v>
-      </c>
       <c r="E27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" t="s">
         <v>51</v>
       </c>
-      <c r="C28" t="s">
-        <v>137</v>
-      </c>
-      <c r="D28" t="s">
-        <v>52</v>
-      </c>
       <c r="E28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" t="s">
         <v>54</v>
       </c>
-      <c r="C30" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" t="s">
-        <v>55</v>
-      </c>
       <c r="E30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" t="s">
         <v>56</v>
       </c>
-      <c r="C31" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" t="s">
-        <v>57</v>
-      </c>
       <c r="E31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" t="s">
         <v>58</v>
       </c>
-      <c r="C32" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" t="s">
-        <v>59</v>
-      </c>
       <c r="E32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" t="s">
         <v>60</v>
       </c>
-      <c r="C33" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" t="s">
-        <v>61</v>
-      </c>
       <c r="E33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" t="s">
         <v>62</v>
       </c>
-      <c r="C34" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" t="s">
-        <v>63</v>
-      </c>
       <c r="E34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" t="s">
         <v>65</v>
       </c>
-      <c r="C35" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" t="s">
-        <v>66</v>
-      </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" t="s">
         <v>67</v>
       </c>
-      <c r="C36" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" t="s">
-        <v>68</v>
-      </c>
       <c r="E36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" t="s">
         <v>71</v>
       </c>
-      <c r="C38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" t="s">
-        <v>72</v>
-      </c>
       <c r="E38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" t="s">
         <v>73</v>
       </c>
-      <c r="C39" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" t="s">
-        <v>74</v>
-      </c>
       <c r="E39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" t="s">
         <v>129</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>130</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>131</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>132</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>133</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>134</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>135</v>
       </c>
-      <c r="H42" t="s">
-        <v>136</v>
-      </c>
       <c r="I42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43" t="s">
         <v>77</v>
       </c>
-      <c r="C43" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" t="s">
-        <v>78</v>
-      </c>
       <c r="E43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" t="s">
         <v>79</v>
       </c>
-      <c r="C44" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" t="s">
-        <v>80</v>
-      </c>
       <c r="E44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" t="s">
         <v>81</v>
       </c>
-      <c r="C45" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" t="s">
-        <v>82</v>
-      </c>
       <c r="E45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46" t="s">
         <v>83</v>
       </c>
-      <c r="C46" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" t="s">
-        <v>84</v>
-      </c>
       <c r="E46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" t="s">
         <v>85</v>
       </c>
-      <c r="C47" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" t="s">
-        <v>86</v>
-      </c>
       <c r="E47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F47" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" t="s">
+        <v>136</v>
+      </c>
+      <c r="D48" t="s">
         <v>87</v>
       </c>
-      <c r="C48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D48" t="s">
-        <v>88</v>
-      </c>
       <c r="E48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>136</v>
+      </c>
+      <c r="D49" t="s">
         <v>89</v>
       </c>
-      <c r="C49" t="s">
-        <v>137</v>
-      </c>
-      <c r="D49" t="s">
-        <v>90</v>
-      </c>
       <c r="E49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" t="s">
         <v>91</v>
       </c>
-      <c r="C50" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" t="s">
-        <v>92</v>
-      </c>
       <c r="E50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" t="s">
         <v>93</v>
       </c>
-      <c r="C51" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" t="s">
-        <v>94</v>
-      </c>
       <c r="E51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" t="s">
         <v>95</v>
       </c>
-      <c r="C52" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" t="s">
-        <v>96</v>
-      </c>
       <c r="E52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D53" t="s">
         <v>97</v>
       </c>
-      <c r="C53" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" t="s">
-        <v>98</v>
-      </c>
       <c r="E53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" t="s">
         <v>99</v>
       </c>
-      <c r="C54" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" t="s">
-        <v>100</v>
-      </c>
       <c r="E54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" t="s">
         <v>129</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>130</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>131</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>132</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>133</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>134</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>135</v>
       </c>
-      <c r="H57" t="s">
-        <v>136</v>
-      </c>
       <c r="I57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D58" t="s">
+        <v>196</v>
+      </c>
+      <c r="E58" t="s">
         <v>197</v>
       </c>
-      <c r="E58" t="s">
-        <v>198</v>
-      </c>
       <c r="F58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s">
         <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E59" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
         <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G60" t="s">
+        <v>227</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="I60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
         <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E62" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F62" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G62" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I62" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E63" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E64" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I64" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E65" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F65" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E66" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F66" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" t="s">
         <v>109</v>
       </c>
-      <c r="C67" t="s">
-        <v>137</v>
-      </c>
-      <c r="D67" t="s">
-        <v>110</v>
-      </c>
       <c r="E67" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F67" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B68" t="s">
+        <v>110</v>
+      </c>
+      <c r="C68" t="s">
+        <v>136</v>
+      </c>
+      <c r="D68" t="s">
         <v>111</v>
       </c>
-      <c r="C68" t="s">
-        <v>137</v>
-      </c>
-      <c r="D68" t="s">
-        <v>112</v>
-      </c>
       <c r="E68" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E69" t="s">
+        <v>197</v>
+      </c>
+      <c r="F69" t="s">
+        <v>181</v>
+      </c>
+      <c r="G69" t="s">
         <v>235</v>
       </c>
-      <c r="E69" t="s">
-        <v>198</v>
-      </c>
-      <c r="F69" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69" t="s">
-        <v>236</v>
-      </c>
       <c r="I69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" t="s">
         <v>129</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>130</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>131</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>132</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>133</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>134</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>135</v>
       </c>
-      <c r="H72" t="s">
-        <v>136</v>
-      </c>
       <c r="I72" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" t="s">
+        <v>136</v>
+      </c>
+      <c r="E73" t="s">
         <v>210</v>
       </c>
-      <c r="B73" t="s">
-        <v>114</v>
-      </c>
-      <c r="C73" t="s">
-        <v>137</v>
-      </c>
-      <c r="E73" t="s">
-        <v>211</v>
-      </c>
       <c r="F73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B74" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D74" t="s">
         <v>115</v>
       </c>
-      <c r="C74" t="s">
-        <v>137</v>
-      </c>
-      <c r="D74" t="s">
-        <v>116</v>
-      </c>
       <c r="E74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B75" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" t="s">
+        <v>136</v>
+      </c>
+      <c r="D75" t="s">
         <v>117</v>
       </c>
-      <c r="C75" t="s">
-        <v>137</v>
-      </c>
-      <c r="D75" t="s">
-        <v>118</v>
-      </c>
       <c r="E75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F76" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B78" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" t="s">
+        <v>136</v>
+      </c>
+      <c r="D78" t="s">
         <v>121</v>
       </c>
-      <c r="C78" t="s">
-        <v>137</v>
-      </c>
-      <c r="D78" t="s">
-        <v>122</v>
-      </c>
       <c r="E78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F78" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B79" t="s">
+        <v>122</v>
+      </c>
+      <c r="C79" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" t="s">
         <v>123</v>
       </c>
-      <c r="C79" t="s">
-        <v>137</v>
-      </c>
-      <c r="D79" t="s">
-        <v>124</v>
-      </c>
       <c r="E79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B80" t="s">
+        <v>124</v>
+      </c>
+      <c r="C80" t="s">
+        <v>136</v>
+      </c>
+      <c r="D80" t="s">
         <v>125</v>
       </c>
-      <c r="C80" t="s">
-        <v>137</v>
-      </c>
-      <c r="D80" t="s">
-        <v>126</v>
-      </c>
       <c r="E80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F80" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B81" t="s">
+        <v>126</v>
+      </c>
+      <c r="C81" t="s">
+        <v>136</v>
+      </c>
+      <c r="D81" t="s">
         <v>127</v>
       </c>
-      <c r="C81" t="s">
-        <v>137</v>
-      </c>
-      <c r="D81" t="s">
-        <v>128</v>
-      </c>
       <c r="E81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F81" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2730,6 +2730,7 @@
     <hyperlink ref="H60" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
     <hyperlink ref="H62" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
     <hyperlink ref="D69" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
+    <hyperlink ref="D18" r:id="rId6" xr:uid="{F28CF6A1-4168-42B7-9C73-DC7334195F2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB046E4A-9BF9-49CD-AE96-9B8590ADBAF3}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{184A50F0-6730-4147-AA65-D4575963E030}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="235">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -158,12 +158,6 @@
     <t>kaulv@prf.cuni.cz</t>
   </si>
   <si>
-    <t>Klusek</t>
-  </si>
-  <si>
-    <t>michal.klusek@prf.cuni.cz</t>
-  </si>
-  <si>
     <t>Koldinská</t>
   </si>
   <si>
@@ -528,9 +522,6 @@
   </si>
   <si>
     <t>Volker Kaul</t>
-  </si>
-  <si>
-    <t>Michal Klusek</t>
   </si>
   <si>
     <t>Kristina Koldinská</t>
@@ -1142,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE358DA8-D777-4377-96EA-27F7BC555635}">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -1150,1093 +1141,1093 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" t="s">
         <v>128</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>130</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>132</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>133</v>
       </c>
-      <c r="G1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H1" t="s">
-        <v>135</v>
-      </c>
       <c r="I1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F10" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F14" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F19" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
         <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F20" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
         <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F22" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
         <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" t="s">
         <v>42</v>
       </c>
-      <c r="C24" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" t="s">
-        <v>43</v>
-      </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F25" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
         <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D27" t="s">
         <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F27" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" t="s">
         <v>50</v>
       </c>
-      <c r="C28" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" t="s">
-        <v>51</v>
-      </c>
       <c r="E28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F28" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
         <v>54</v>
       </c>
       <c r="E30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
         <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
         <v>56</v>
       </c>
       <c r="E31" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s">
         <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
         <v>58</v>
       </c>
       <c r="E32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s">
         <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
         <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F33" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F34" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s">
         <v>64</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
         <v>65</v>
       </c>
       <c r="E35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F35" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s">
         <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F36" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
         <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>134</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F37" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
         <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
         <v>71</v>
       </c>
       <c r="E38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F38" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>180</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>136</v>
-      </c>
-      <c r="D39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E39" t="s">
-        <v>137</v>
-      </c>
-      <c r="F39" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>126</v>
+      </c>
+      <c r="B41" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" t="s">
+        <v>132</v>
+      </c>
+      <c r="H41" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="E42" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="F42" t="s">
-        <v>133</v>
-      </c>
-      <c r="G42" t="s">
-        <v>134</v>
-      </c>
-      <c r="H42" t="s">
-        <v>135</v>
-      </c>
-      <c r="I42" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D43" t="s">
         <v>77</v>
       </c>
       <c r="E43" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F43" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B44" t="s">
         <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
         <v>79</v>
       </c>
       <c r="E44" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F44" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B45" t="s">
         <v>80</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
         <v>81</v>
       </c>
       <c r="E45" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B46" t="s">
         <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s">
         <v>83</v>
       </c>
       <c r="E46" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F46" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B47" t="s">
         <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D47" t="s">
         <v>85</v>
       </c>
       <c r="E47" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F47" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
         <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D48" t="s">
         <v>87</v>
       </c>
       <c r="E48" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F48" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s">
         <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D49" t="s">
         <v>89</v>
       </c>
       <c r="E49" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F49" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
         <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D50" t="s">
         <v>91</v>
       </c>
       <c r="E50" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F50" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
         <v>92</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D51" t="s">
         <v>93</v>
       </c>
       <c r="E51" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F51" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B52" t="s">
         <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D52" t="s">
         <v>95</v>
       </c>
       <c r="E52" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F52" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s">
         <v>96</v>
       </c>
       <c r="C53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D53" t="s">
         <v>97</v>
       </c>
       <c r="E53" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F53" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>194</v>
-      </c>
-      <c r="B54" t="s">
-        <v>98</v>
-      </c>
-      <c r="C54" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" t="s">
-        <v>99</v>
-      </c>
-      <c r="E54" t="s">
-        <v>182</v>
-      </c>
-      <c r="F54" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" t="s">
+        <v>129</v>
+      </c>
+      <c r="E56" t="s">
+        <v>130</v>
+      </c>
+      <c r="F56" t="s">
+        <v>131</v>
+      </c>
+      <c r="G56" t="s">
+        <v>132</v>
+      </c>
+      <c r="H56" t="s">
+        <v>133</v>
+      </c>
+      <c r="I56" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="E57" t="s">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="F57" t="s">
-        <v>133</v>
-      </c>
-      <c r="G57" t="s">
-        <v>134</v>
-      </c>
-      <c r="H57" t="s">
-        <v>135</v>
-      </c>
-      <c r="I57" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
@@ -2244,492 +2235,472 @@
         <v>195</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D58" t="s">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="E58" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F58" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="H58" t="s">
+        <v>220</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E59" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F59" t="s">
-        <v>181</v>
-      </c>
-      <c r="H59" t="s">
-        <v>223</v>
-      </c>
-      <c r="I59" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G59" t="s">
+        <v>224</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>225</v>
+      </c>
+      <c r="I59" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E60" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F60" t="s">
-        <v>181</v>
-      </c>
-      <c r="G60" t="s">
-        <v>227</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I60" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E61" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F61" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="G61" t="s">
+        <v>227</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I61" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E62" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F62" t="s">
-        <v>181</v>
-      </c>
-      <c r="G62" t="s">
-        <v>230</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="I62" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E63" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F63" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I63" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D64" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E64" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F64" t="s">
-        <v>181</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="I64" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E65" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F65" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s">
         <v>107</v>
       </c>
       <c r="E66" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F66" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B67" t="s">
         <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
       </c>
       <c r="E67" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F67" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B68" t="s">
         <v>110</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
-      </c>
-      <c r="D68" t="s">
-        <v>111</v>
+        <v>134</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="E68" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F68" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>208</v>
-      </c>
-      <c r="B69" t="s">
-        <v>112</v>
-      </c>
-      <c r="C69" t="s">
-        <v>136</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E69" t="s">
-        <v>197</v>
-      </c>
-      <c r="F69" t="s">
-        <v>181</v>
-      </c>
-      <c r="G69" t="s">
-        <v>235</v>
-      </c>
-      <c r="I69" t="s">
-        <v>231</v>
+        <v>178</v>
+      </c>
+      <c r="G68" t="s">
+        <v>232</v>
+      </c>
+      <c r="I68" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>222</v>
+        <v>126</v>
+      </c>
+      <c r="B71" t="s">
+        <v>127</v>
+      </c>
+      <c r="C71" t="s">
+        <v>128</v>
+      </c>
+      <c r="D71" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" t="s">
+        <v>130</v>
+      </c>
+      <c r="F71" t="s">
+        <v>131</v>
+      </c>
+      <c r="G71" t="s">
+        <v>132</v>
+      </c>
+      <c r="H71" t="s">
+        <v>133</v>
+      </c>
+      <c r="I71" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
-      </c>
-      <c r="D72" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E72" t="s">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
-      </c>
-      <c r="G72" t="s">
-        <v>134</v>
-      </c>
-      <c r="H72" t="s">
-        <v>135</v>
-      </c>
-      <c r="I72" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B73" t="s">
+        <v>112</v>
+      </c>
+      <c r="C73" t="s">
+        <v>134</v>
+      </c>
+      <c r="D73" t="s">
         <v>113</v>
       </c>
-      <c r="C73" t="s">
-        <v>136</v>
-      </c>
       <c r="E73" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F73" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B74" t="s">
         <v>114</v>
       </c>
       <c r="C74" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
         <v>115</v>
       </c>
       <c r="E74" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F74" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B75" t="s">
         <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>136</v>
-      </c>
-      <c r="D75" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E75" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F75" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B76" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C76" t="s">
-        <v>136</v>
+        <v>134</v>
+      </c>
+      <c r="D76" t="s">
+        <v>117</v>
       </c>
       <c r="E76" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F76" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C77" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D77" t="s">
         <v>119</v>
       </c>
       <c r="E77" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F77" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B78" t="s">
         <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D78" t="s">
         <v>121</v>
       </c>
       <c r="E78" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F78" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B79" t="s">
         <v>122</v>
       </c>
       <c r="C79" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D79" t="s">
         <v>123</v>
       </c>
       <c r="E79" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F79" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B80" t="s">
         <v>124</v>
       </c>
       <c r="C80" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D80" t="s">
         <v>125</v>
       </c>
       <c r="E80" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F80" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>218</v>
-      </c>
-      <c r="B81" t="s">
-        <v>126</v>
-      </c>
-      <c r="C81" t="s">
-        <v>136</v>
-      </c>
-      <c r="D81" t="s">
-        <v>127</v>
-      </c>
-      <c r="E81" t="s">
-        <v>210</v>
-      </c>
-      <c r="F81" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I59" r:id="rId1" tooltip="Adam_Geršl.jpg" display="https://github.com/kpp-sketch/cios_website/blob/main/public/Adam_Ger%C5%A1l.jpg" xr:uid="{D50D89A4-5891-490B-BEF1-EA3A0BBB4952}"/>
-    <hyperlink ref="H64" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
-    <hyperlink ref="H60" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
-    <hyperlink ref="H62" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
-    <hyperlink ref="D69" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
+    <hyperlink ref="I58" r:id="rId1" tooltip="Adam_Geršl.jpg" display="https://github.com/kpp-sketch/cios_website/blob/main/public/Adam_Ger%C5%A1l.jpg" xr:uid="{D50D89A4-5891-490B-BEF1-EA3A0BBB4952}"/>
+    <hyperlink ref="H63" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
+    <hyperlink ref="H59" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
+    <hyperlink ref="H61" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
+    <hyperlink ref="D68" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
     <hyperlink ref="D18" r:id="rId6" xr:uid="{F28CF6A1-4168-42B7-9C73-DC7334195F2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{184A50F0-6730-4147-AA65-D4575963E030}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A6C489D-5E5F-49B0-AE87-3072B8EA0EC6}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="229">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -203,12 +203,6 @@
     <t>ondrejek@prf.cuni.cz</t>
   </si>
   <si>
-    <t>Orsini</t>
-  </si>
-  <si>
-    <t>eliska.orsini@prf.cuni.cz</t>
-  </si>
-  <si>
     <t>Sharma</t>
   </si>
   <si>
@@ -224,12 +218,6 @@
     <t>Sivá</t>
   </si>
   <si>
-    <t>Startlová</t>
-  </si>
-  <si>
-    <t>patricie.startlova@prf.cuni.cz</t>
-  </si>
-  <si>
     <t>Šoltés</t>
   </si>
   <si>
@@ -548,16 +536,10 @@
     <t>Pavel Ondřejek</t>
   </si>
   <si>
-    <t>Eliška Orsini</t>
-  </si>
-  <si>
     <t>Nishtha Sharma</t>
   </si>
   <si>
     <t>Zoltán Páll</t>
-  </si>
-  <si>
-    <t>Patricie Startlová</t>
   </si>
   <si>
     <t>Michal Šoltés</t>
@@ -1133,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE358DA8-D777-4377-96EA-27F7BC555635}">
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -1141,1566 +1123,1526 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
         <v>126</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>127</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>128</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>129</v>
       </c>
-      <c r="E1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" t="s">
-        <v>133</v>
-      </c>
       <c r="I1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F6" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F7" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
         <v>134</v>
       </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F9" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F11" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F14" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F15" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F16" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F19" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
         <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F20" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
         <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F21" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
         <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F24" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F25" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F26" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
         <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>50</v>
       </c>
       <c r="E28" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F29" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>54</v>
       </c>
       <c r="E30" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F30" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
         <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
         <v>56</v>
       </c>
       <c r="E31" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F31" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s">
         <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
         <v>58</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F32" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
         <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F34" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
         <v>64</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
         <v>65</v>
       </c>
       <c r="E35" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F35" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B36" t="s">
         <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>130</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>176</v>
-      </c>
-      <c r="B37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" t="s">
-        <v>134</v>
-      </c>
-      <c r="D37" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" t="s">
-        <v>135</v>
-      </c>
-      <c r="F37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" t="s">
-        <v>134</v>
-      </c>
-      <c r="D38" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F38" t="s">
-        <v>178</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" t="s">
+        <v>126</v>
+      </c>
+      <c r="F39" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H39" t="s">
+        <v>129</v>
+      </c>
+      <c r="I39" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>174</v>
+      </c>
+      <c r="B40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="F41" t="s">
-        <v>131</v>
-      </c>
-      <c r="G41" t="s">
-        <v>132</v>
-      </c>
-      <c r="H41" t="s">
-        <v>133</v>
-      </c>
-      <c r="I41" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B42" t="s">
         <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
         <v>75</v>
       </c>
       <c r="E42" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F42" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B43" t="s">
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D43" t="s">
         <v>77</v>
       </c>
       <c r="E43" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F43" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B44" t="s">
         <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
         <v>79</v>
       </c>
       <c r="E44" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F44" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B45" t="s">
         <v>80</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D45" t="s">
         <v>81</v>
       </c>
       <c r="E45" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F45" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B46" t="s">
         <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D46" t="s">
         <v>83</v>
       </c>
       <c r="E46" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F46" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B47" t="s">
         <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
         <v>85</v>
       </c>
       <c r="E47" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F47" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B48" t="s">
         <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D48" t="s">
         <v>87</v>
       </c>
       <c r="E48" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F48" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B49" t="s">
         <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
         <v>89</v>
       </c>
       <c r="E49" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F49" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
         <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
         <v>91</v>
       </c>
       <c r="E50" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F50" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
         <v>92</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D51" t="s">
         <v>93</v>
       </c>
       <c r="E51" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F51" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>190</v>
-      </c>
-      <c r="B52" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" t="s">
-        <v>134</v>
-      </c>
-      <c r="D52" t="s">
-        <v>95</v>
-      </c>
-      <c r="E52" t="s">
-        <v>179</v>
-      </c>
-      <c r="F52" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>191</v>
-      </c>
-      <c r="B53" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" t="s">
-        <v>134</v>
-      </c>
-      <c r="D53" t="s">
-        <v>97</v>
-      </c>
-      <c r="E53" t="s">
-        <v>179</v>
-      </c>
-      <c r="F53" t="s">
-        <v>178</v>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" t="s">
+        <v>127</v>
+      </c>
+      <c r="G54" t="s">
+        <v>128</v>
+      </c>
+      <c r="H54" t="s">
+        <v>129</v>
+      </c>
+      <c r="I54" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>186</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>130</v>
+      </c>
+      <c r="D55" t="s">
+        <v>187</v>
+      </c>
+      <c r="E55" t="s">
+        <v>188</v>
+      </c>
+      <c r="F55" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E56" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="F56" t="s">
-        <v>131</v>
-      </c>
-      <c r="G56" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="H56" t="s">
-        <v>133</v>
-      </c>
-      <c r="I56" t="s">
-        <v>221</v>
+        <v>214</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D57" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="E57" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F57" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="G57" t="s">
+        <v>218</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I57" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D58" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E58" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F58" t="s">
-        <v>178</v>
-      </c>
-      <c r="H58" t="s">
-        <v>220</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E59" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F59" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G59" t="s">
+        <v>221</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="I59" t="s">
         <v>224</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I59" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D60" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F60" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C61" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E61" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F61" t="s">
-        <v>178</v>
-      </c>
-      <c r="G61" t="s">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="I61" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E62" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F62" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D63" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F63" t="s">
-        <v>178</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="I63" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E64" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F64" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D65" t="s">
         <v>105</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F65" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B66" t="s">
         <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
-      </c>
-      <c r="D66" t="s">
-        <v>107</v>
+        <v>130</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="E66" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F66" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>204</v>
-      </c>
-      <c r="B67" t="s">
-        <v>108</v>
-      </c>
-      <c r="C67" t="s">
-        <v>134</v>
-      </c>
-      <c r="D67" t="s">
-        <v>109</v>
-      </c>
-      <c r="E67" t="s">
-        <v>194</v>
-      </c>
-      <c r="F67" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="G66" t="s">
+        <v>226</v>
+      </c>
+      <c r="I66" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>205</v>
-      </c>
-      <c r="B68" t="s">
-        <v>110</v>
-      </c>
-      <c r="C68" t="s">
-        <v>134</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E68" t="s">
-        <v>194</v>
-      </c>
-      <c r="F68" t="s">
-        <v>178</v>
-      </c>
-      <c r="G68" t="s">
-        <v>232</v>
-      </c>
-      <c r="I68" t="s">
-        <v>228</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>122</v>
+      </c>
+      <c r="B69" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" t="s">
+        <v>126</v>
+      </c>
+      <c r="F69" t="s">
+        <v>127</v>
+      </c>
+      <c r="G69" t="s">
+        <v>128</v>
+      </c>
+      <c r="H69" t="s">
+        <v>129</v>
+      </c>
+      <c r="I69" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>219</v>
+        <v>200</v>
+      </c>
+      <c r="B70" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" t="s">
+        <v>130</v>
+      </c>
+      <c r="E70" t="s">
+        <v>201</v>
+      </c>
+      <c r="F70" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D71" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E71" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="F71" t="s">
-        <v>131</v>
-      </c>
-      <c r="G71" t="s">
-        <v>132</v>
-      </c>
-      <c r="H71" t="s">
-        <v>133</v>
-      </c>
-      <c r="I71" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B72" t="s">
+        <v>110</v>
+      </c>
+      <c r="C72" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" t="s">
         <v>111</v>
       </c>
-      <c r="C72" t="s">
-        <v>134</v>
-      </c>
       <c r="E72" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F72" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B73" t="s">
         <v>112</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
-      </c>
-      <c r="D73" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E73" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F73" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B74" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D74" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F74" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B75" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
+        <v>130</v>
+      </c>
+      <c r="D75" t="s">
+        <v>115</v>
       </c>
       <c r="E75" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F75" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D76" t="s">
         <v>117</v>
       </c>
       <c r="E76" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F76" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B77" t="s">
         <v>118</v>
       </c>
       <c r="C77" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D77" t="s">
         <v>119</v>
       </c>
       <c r="E77" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F77" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B78" t="s">
         <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D78" t="s">
         <v>121</v>
       </c>
       <c r="E78" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F78" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>214</v>
-      </c>
-      <c r="B79" t="s">
-        <v>122</v>
-      </c>
-      <c r="C79" t="s">
-        <v>134</v>
-      </c>
-      <c r="D79" t="s">
-        <v>123</v>
-      </c>
-      <c r="E79" t="s">
-        <v>207</v>
-      </c>
-      <c r="F79" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>215</v>
-      </c>
-      <c r="B80" t="s">
-        <v>124</v>
-      </c>
-      <c r="C80" t="s">
-        <v>134</v>
-      </c>
-      <c r="D80" t="s">
-        <v>125</v>
-      </c>
-      <c r="E80" t="s">
-        <v>207</v>
-      </c>
-      <c r="F80" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I58" r:id="rId1" tooltip="Adam_Geršl.jpg" display="https://github.com/kpp-sketch/cios_website/blob/main/public/Adam_Ger%C5%A1l.jpg" xr:uid="{D50D89A4-5891-490B-BEF1-EA3A0BBB4952}"/>
-    <hyperlink ref="H63" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
-    <hyperlink ref="H59" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
-    <hyperlink ref="H61" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
-    <hyperlink ref="D68" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
+    <hyperlink ref="I56" r:id="rId1" tooltip="Adam_Geršl.jpg" display="https://github.com/kpp-sketch/cios_website/blob/main/public/Adam_Ger%C5%A1l.jpg" xr:uid="{D50D89A4-5891-490B-BEF1-EA3A0BBB4952}"/>
+    <hyperlink ref="H61" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
+    <hyperlink ref="H57" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
+    <hyperlink ref="H59" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
+    <hyperlink ref="D66" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
     <hyperlink ref="D18" r:id="rId6" xr:uid="{F28CF6A1-4168-42B7-9C73-DC7334195F2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A6C489D-5E5F-49B0-AE87-3072B8EA0EC6}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A06030D-F3D2-4CE4-BF82-233F7264F3D1}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -692,9 +692,6 @@
     <t>https://ies.fsv.cuni.cz/contacts/institute-members/95375215</t>
   </si>
   <si>
-    <t xml:space="preserve">Roman Horvath is Professor at the Institute of Economic Studies, Faculty of Social Sciences, Charles University in Prague. He previously served as Head of the Research Unit and Advisor to the Board at the Czech National Bank, and as President of the Czech Economic Society. His research has been published in leading journals including the Journal of International Economics, IMF Economic Review, Journal of Money, Credit and Banking, Review of Economic Dynamics, World Development, and the World Bank Economic Review, among many others. He is Associate Editor of the Journal of Financial Stability and serves on the Board of Advisors of Open Economies Review. He has also acted as a consultant to several institutions, including the European Parliament, where he was a member of the Monetary Experts Panel, and the World Bank.  </t>
-  </si>
-  <si>
     <t>https://ies.fsv.cuni.cz/en/contacts/institute-members/59321289</t>
   </si>
   <si>
@@ -723,6 +720,9 @@
   </si>
   <si>
     <t>fjelinek@prf.cuni.cz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman Horvath is Professor at the Institute of Economic Studies, Faculty of Social Sciences, Charles University in Prague. He previously served as Head of the Research Unit and Advisor to the Board at the Czech National Bank, and as President of the Czech Economic Society. His research has been published in leading journals. He is Associate Editor of the Journal of Financial Stability and serves on the Board of Advisors of Open Economies Review. He has also acted as a consultant to several institutions, including the European Parliament, where he was a member of the Monetary Experts Panel, and the World Bank.  </t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1478,7 @@
         <v>130</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E18" t="s">
         <v>131</v>
@@ -2218,13 +2218,13 @@
         <v>172</v>
       </c>
       <c r="G57" t="s">
+        <v>228</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="I57" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
@@ -2267,13 +2267,13 @@
         <v>172</v>
       </c>
       <c r="G59" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -2319,7 +2319,7 @@
         <v>217</v>
       </c>
       <c r="I61" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
@@ -2413,7 +2413,7 @@
         <v>130</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E66" t="s">
         <v>188</v>
@@ -2422,10 +2422,10 @@
         <v>172</v>
       </c>
       <c r="G66" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I66" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A06030D-F3D2-4CE4-BF82-233F7264F3D1}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77264709-FD4C-444B-B671-049649754291}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="232">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -723,6 +723,15 @@
   </si>
   <si>
     <t xml:space="preserve">Roman Horvath is Professor at the Institute of Economic Studies, Faculty of Social Sciences, Charles University in Prague. He previously served as Head of the Research Unit and Advisor to the Board at the Czech National Bank, and as President of the Czech Economic Society. His research has been published in leading journals. He is Associate Editor of the Journal of Financial Stability and serves on the Board of Advisors of Open Economies Review. He has also acted as a consultant to several institutions, including the European Parliament, where he was a member of the Monetary Experts Panel, and the World Bank.  </t>
+  </si>
+  <si>
+    <t>Edin Hodžić</t>
+  </si>
+  <si>
+    <t>Hodžić</t>
+  </si>
+  <si>
+    <t>edin.hodzic@prf.cuni.cz</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE358DA8-D777-4377-96EA-27F7BC555635}">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -1449,16 +1458,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
         <v>130</v>
       </c>
-      <c r="D17" t="s">
-        <v>28</v>
+      <c r="D17" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="E17" t="s">
         <v>131</v>
@@ -1469,16 +1478,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>227</v>
+      <c r="D18" t="s">
+        <v>28</v>
       </c>
       <c r="E18" t="s">
         <v>131</v>
@@ -1489,16 +1498,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>130</v>
       </c>
-      <c r="D19" t="s">
-        <v>33</v>
+      <c r="D19" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="E19" t="s">
         <v>131</v>
@@ -1509,16 +1518,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
         <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
         <v>131</v>
@@ -1529,16 +1538,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
         <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
         <v>131</v>
@@ -1549,16 +1558,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
         <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
         <v>131</v>
@@ -1569,16 +1578,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
         <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
         <v>131</v>
@@ -1589,16 +1598,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>130</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
         <v>131</v>
@@ -1609,16 +1618,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="C25" t="s">
         <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
         <v>131</v>
@@ -1629,16 +1638,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
         <v>131</v>
@@ -1649,16 +1658,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
         <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
         <v>131</v>
@@ -1669,16 +1678,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
         <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
         <v>131</v>
@@ -1689,16 +1698,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
         <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
         <v>131</v>
@@ -1709,16 +1718,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
         <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
         <v>131</v>
@@ -1729,16 +1738,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
         <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
         <v>131</v>
@@ -1749,16 +1758,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
         <v>131</v>
@@ -1769,16 +1778,16 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
         <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s">
         <v>131</v>
@@ -1789,13 +1798,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
         <v>130</v>
+      </c>
+      <c r="D34" t="s">
+        <v>61</v>
       </c>
       <c r="E34" t="s">
         <v>131</v>
@@ -1806,16 +1818,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C35" t="s">
         <v>130</v>
-      </c>
-      <c r="D35" t="s">
-        <v>65</v>
       </c>
       <c r="E35" t="s">
         <v>131</v>
@@ -1826,90 +1835,90 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>171</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>66</v>
       </c>
-      <c r="C36" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C37" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" t="s">
         <v>67</v>
       </c>
-      <c r="E36" t="s">
-        <v>131</v>
-      </c>
-      <c r="F36" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>211</v>
+      <c r="E37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" t="s">
-        <v>126</v>
-      </c>
-      <c r="F39" t="s">
-        <v>127</v>
-      </c>
-      <c r="G39" t="s">
-        <v>128</v>
-      </c>
-      <c r="H39" t="s">
-        <v>129</v>
-      </c>
-      <c r="I39" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F40" t="s">
-        <v>172</v>
+        <v>127</v>
+      </c>
+      <c r="G40" t="s">
+        <v>128</v>
+      </c>
+      <c r="H40" t="s">
+        <v>129</v>
+      </c>
+      <c r="I40" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
         <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E41" t="s">
         <v>173</v>
@@ -1920,16 +1929,16 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
         <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E42" t="s">
         <v>173</v>
@@ -1940,16 +1949,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
         <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E43" t="s">
         <v>173</v>
@@ -1960,16 +1969,16 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C44" t="s">
         <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E44" t="s">
         <v>173</v>
@@ -1980,16 +1989,16 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
         <v>130</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E45" t="s">
         <v>173</v>
@@ -2000,16 +2009,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C46" t="s">
         <v>130</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E46" t="s">
         <v>173</v>
@@ -2020,16 +2029,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C47" t="s">
         <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
         <v>173</v>
@@ -2040,16 +2049,16 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
         <v>130</v>
       </c>
       <c r="D48" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E48" t="s">
         <v>173</v>
@@ -2060,16 +2069,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
         <v>130</v>
       </c>
       <c r="D49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E49" t="s">
         <v>173</v>
@@ -2080,16 +2089,16 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
         <v>130</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E50" t="s">
         <v>173</v>
@@ -2100,16 +2109,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
         <v>130</v>
       </c>
       <c r="D51" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E51" t="s">
         <v>173</v>
@@ -2118,72 +2127,72 @@
         <v>172</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>212</v>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" t="s">
-        <v>123</v>
-      </c>
-      <c r="C54" t="s">
-        <v>124</v>
-      </c>
-      <c r="D54" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" t="s">
-        <v>126</v>
-      </c>
-      <c r="F54" t="s">
-        <v>127</v>
-      </c>
-      <c r="G54" t="s">
-        <v>128</v>
-      </c>
-      <c r="H54" t="s">
-        <v>129</v>
-      </c>
-      <c r="I54" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D55" t="s">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="E55" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="F55" t="s">
-        <v>172</v>
+        <v>127</v>
+      </c>
+      <c r="G55" t="s">
+        <v>128</v>
+      </c>
+      <c r="H55" t="s">
+        <v>129</v>
+      </c>
+      <c r="I55" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
         <v>130</v>
       </c>
       <c r="D56" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
         <v>188</v>
@@ -2191,25 +2200,19 @@
       <c r="F56" t="s">
         <v>172</v>
       </c>
-      <c r="H56" t="s">
-        <v>214</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>216</v>
-      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
         <v>130</v>
       </c>
       <c r="D57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E57" t="s">
         <v>188</v>
@@ -2217,28 +2220,25 @@
       <c r="F57" t="s">
         <v>172</v>
       </c>
-      <c r="G57" t="s">
-        <v>228</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I57" t="s">
-        <v>226</v>
+      <c r="H57" t="s">
+        <v>214</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
         <v>130</v>
       </c>
       <c r="D58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E58" t="s">
         <v>188</v>
@@ -2246,19 +2246,28 @@
       <c r="F58" t="s">
         <v>172</v>
       </c>
+      <c r="G58" t="s">
+        <v>228</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I58" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
         <v>130</v>
       </c>
       <c r="D59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E59" t="s">
         <v>188</v>
@@ -2266,28 +2275,19 @@
       <c r="F59" t="s">
         <v>172</v>
       </c>
-      <c r="G59" t="s">
-        <v>220</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I59" t="s">
-        <v>223</v>
-      </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C60" t="s">
         <v>130</v>
       </c>
       <c r="D60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E60" t="s">
         <v>188</v>
@@ -2295,19 +2295,28 @@
       <c r="F60" t="s">
         <v>172</v>
       </c>
+      <c r="G60" t="s">
+        <v>220</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I60" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C61" t="s">
         <v>130</v>
       </c>
       <c r="D61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E61" t="s">
         <v>188</v>
@@ -2315,25 +2324,19 @@
       <c r="F61" t="s">
         <v>172</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="I61" t="s">
-        <v>222</v>
-      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
         <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E62" t="s">
         <v>188</v>
@@ -2341,19 +2344,25 @@
       <c r="F62" t="s">
         <v>172</v>
       </c>
+      <c r="H62" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I62" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63" t="s">
         <v>130</v>
       </c>
       <c r="D63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E63" t="s">
         <v>188</v>
@@ -2364,16 +2373,16 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B64" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
         <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E64" t="s">
         <v>188</v>
@@ -2384,16 +2393,16 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C65" t="s">
         <v>130</v>
       </c>
       <c r="D65" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E65" t="s">
         <v>188</v>
@@ -2404,16 +2413,16 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
         <v>130</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>224</v>
+      <c r="D66" t="s">
+        <v>105</v>
       </c>
       <c r="E66" t="s">
         <v>188</v>
@@ -2421,76 +2430,76 @@
       <c r="F66" t="s">
         <v>172</v>
       </c>
-      <c r="G66" t="s">
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F67" t="s">
+        <v>172</v>
+      </c>
+      <c r="G67" t="s">
         <v>225</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I67" t="s">
         <v>221</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>122</v>
-      </c>
-      <c r="B69" t="s">
-        <v>123</v>
-      </c>
-      <c r="C69" t="s">
-        <v>124</v>
-      </c>
-      <c r="D69" t="s">
-        <v>125</v>
-      </c>
-      <c r="E69" t="s">
-        <v>126</v>
-      </c>
-      <c r="F69" t="s">
-        <v>127</v>
-      </c>
-      <c r="G69" t="s">
-        <v>128</v>
-      </c>
-      <c r="H69" t="s">
-        <v>129</v>
-      </c>
-      <c r="I69" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C70" t="s">
-        <v>130</v>
+        <v>124</v>
+      </c>
+      <c r="D70" t="s">
+        <v>125</v>
       </c>
       <c r="E70" t="s">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="F70" t="s">
-        <v>172</v>
+        <v>127</v>
+      </c>
+      <c r="G70" t="s">
+        <v>128</v>
+      </c>
+      <c r="H70" t="s">
+        <v>129</v>
+      </c>
+      <c r="I70" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C71" t="s">
         <v>130</v>
-      </c>
-      <c r="D71" t="s">
-        <v>109</v>
       </c>
       <c r="E71" t="s">
         <v>201</v>
@@ -2501,16 +2510,16 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B72" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
         <v>130</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E72" t="s">
         <v>201</v>
@@ -2521,13 +2530,16 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B73" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C73" t="s">
         <v>130</v>
+      </c>
+      <c r="D73" t="s">
+        <v>111</v>
       </c>
       <c r="E73" t="s">
         <v>201</v>
@@ -2538,16 +2550,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
         <v>130</v>
-      </c>
-      <c r="D74" t="s">
-        <v>113</v>
       </c>
       <c r="E74" t="s">
         <v>201</v>
@@ -2558,16 +2567,16 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="C75" t="s">
         <v>130</v>
       </c>
       <c r="D75" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E75" t="s">
         <v>201</v>
@@ -2578,16 +2587,16 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
         <v>130</v>
       </c>
       <c r="D76" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E76" t="s">
         <v>201</v>
@@ -2598,16 +2607,16 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B77" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
         <v>130</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E77" t="s">
         <v>201</v>
@@ -2618,16 +2627,16 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
         <v>130</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E78" t="s">
         <v>201</v>
@@ -2636,14 +2645,35 @@
         <v>172</v>
       </c>
     </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>209</v>
+      </c>
+      <c r="B79" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" t="s">
+        <v>130</v>
+      </c>
+      <c r="D79" t="s">
+        <v>121</v>
+      </c>
+      <c r="E79" t="s">
+        <v>201</v>
+      </c>
+      <c r="F79" t="s">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I56" r:id="rId1" tooltip="Adam_Geršl.jpg" display="https://github.com/kpp-sketch/cios_website/blob/main/public/Adam_Ger%C5%A1l.jpg" xr:uid="{D50D89A4-5891-490B-BEF1-EA3A0BBB4952}"/>
-    <hyperlink ref="H61" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
-    <hyperlink ref="H57" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
-    <hyperlink ref="H59" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
-    <hyperlink ref="D66" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
-    <hyperlink ref="D18" r:id="rId6" xr:uid="{F28CF6A1-4168-42B7-9C73-DC7334195F2B}"/>
+    <hyperlink ref="I57" r:id="rId1" tooltip="Adam_Geršl.jpg" display="https://github.com/kpp-sketch/cios_website/blob/main/public/Adam_Ger%C5%A1l.jpg" xr:uid="{D50D89A4-5891-490B-BEF1-EA3A0BBB4952}"/>
+    <hyperlink ref="H62" r:id="rId2" xr:uid="{0595607A-DFBF-47A5-8038-98AF033653C1}"/>
+    <hyperlink ref="H58" r:id="rId3" xr:uid="{D7AB2470-9538-4E87-9694-52C8A464BD61}"/>
+    <hyperlink ref="H60" r:id="rId4" xr:uid="{D027D077-C84D-453F-AD91-5C622F9EA877}"/>
+    <hyperlink ref="D67" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
+    <hyperlink ref="D19" r:id="rId6" xr:uid="{F28CF6A1-4168-42B7-9C73-DC7334195F2B}"/>
+    <hyperlink ref="D17" r:id="rId7" xr:uid="{24AA546C-6CCE-49CE-9B7B-A5ABBEA6023C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77264709-FD4C-444B-B671-049649754291}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9751B505-4DD2-4FEB-A895-7FEB89232A70}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="235">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -732,6 +732,15 @@
   </si>
   <si>
     <t>edin.hodzic@prf.cuni.cz</t>
+  </si>
+  <si>
+    <t>Data Steward</t>
+  </si>
+  <si>
+    <t>Karolina has been providing advisory on data protection and data management aspects of data handling in scientific research for over five years. She acts as a Data Steward and Open Science Coordinator at the Faculty of Law, Charles University, and previously held the position of Data Protection Officer for criminology research at the Institute of State and Law of the Czech Academy of Sciences.</t>
+  </si>
+  <si>
+    <t>karolina_martinek.png</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1465,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>229</v>
       </c>
@@ -1476,7 +1485,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>153</v>
       </c>
@@ -1496,7 +1505,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>154</v>
       </c>
@@ -1516,7 +1525,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>210</v>
       </c>
@@ -1536,7 +1545,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>155</v>
       </c>
@@ -1556,7 +1565,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>156</v>
       </c>
@@ -1576,7 +1585,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>157</v>
       </c>
@@ -1596,7 +1605,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>158</v>
       </c>
@@ -1616,7 +1625,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>159</v>
       </c>
@@ -1636,7 +1645,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>160</v>
       </c>
@@ -1644,7 +1653,7 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="D26" t="s">
         <v>45</v>
@@ -1655,8 +1664,14 @@
       <c r="F26" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" t="s">
+        <v>233</v>
+      </c>
+      <c r="I26" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>161</v>
       </c>
@@ -1676,7 +1691,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>162</v>
       </c>
@@ -1696,7 +1711,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>163</v>
       </c>
@@ -1716,7 +1731,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>164</v>
       </c>
@@ -1736,7 +1751,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>165</v>
       </c>
@@ -1756,7 +1771,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>166</v>
       </c>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9751B505-4DD2-4FEB-A895-7FEB89232A70}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F44BCE-BFBF-491E-B92D-F62FE637E8B1}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="237">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -741,6 +741,12 @@
   </si>
   <si>
     <t>karolina_martinek.png</t>
+  </si>
+  <si>
+    <t>marek_antos.jpg</t>
+  </si>
+  <si>
+    <t>Associate Professor at the Faculty of Law, Charles University. His academic research explores a broad spectrum of constitutional law. He is particularly interested in elections, electoral systems, and the financing of political parties. Recently, his research has also focused on constitutional conventions and unwritten rules within Central European constitutional systems. Additionally, he extensively studies the constitutional implications of technological development, internet governance, and the protection of human rights in the digital era.</t>
   </si>
 </sst>
 </file>
@@ -1207,6 +1213,12 @@
       <c r="F3" t="s">
         <v>172</v>
       </c>
+      <c r="G3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I3" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F44BCE-BFBF-491E-B92D-F62FE637E8B1}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B33F82-6151-4EE4-A5F2-FE8FBEF5224E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="239">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -747,6 +747,12 @@
   </si>
   <si>
     <t>Associate Professor at the Faculty of Law, Charles University. His academic research explores a broad spectrum of constitutional law. He is particularly interested in elections, electoral systems, and the financing of political parties. Recently, his research has also focused on constitutional conventions and unwritten rules within Central European constitutional systems. Additionally, he extensively studies the constitutional implications of technological development, internet governance, and the protection of human rights in the digital era.</t>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/msoltes/home</t>
+  </si>
+  <si>
+    <t>michal_soltes.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1842,6 +1848,15 @@
       <c r="F34" t="s">
         <v>172</v>
       </c>
+      <c r="G34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I34" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -2701,6 +2716,7 @@
     <hyperlink ref="D67" r:id="rId5" xr:uid="{D6A5AA73-B2A0-4841-8488-7DA548470612}"/>
     <hyperlink ref="D19" r:id="rId6" xr:uid="{F28CF6A1-4168-42B7-9C73-DC7334195F2B}"/>
     <hyperlink ref="D17" r:id="rId7" xr:uid="{24AA546C-6CCE-49CE-9B7B-A5ABBEA6023C}"/>
+    <hyperlink ref="H34" r:id="rId8" tooltip="https://sites.google.com/view/msoltes/home" xr:uid="{ED89B3E5-CB58-4B08-937D-91DE2FB52B16}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B33F82-6151-4EE4-A5F2-FE8FBEF5224E}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A00893EE-034A-4A94-BD6D-2EA95DBEE601}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="242">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -515,9 +515,6 @@
     <t>Kristina Koldinská</t>
   </si>
   <si>
-    <t>William King LeRoy</t>
-  </si>
-  <si>
     <t>Karolína Martínek (Nová)</t>
   </si>
   <si>
@@ -753,13 +750,25 @@
   </si>
   <si>
     <t>michal_soltes.jpeg</t>
+  </si>
+  <si>
+    <t>William LeRoy</t>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/william-leroy/home</t>
+  </si>
+  <si>
+    <t>william_leroy.jpg</t>
+  </si>
+  <si>
+    <t>I am an empirical social scientist studying the effects of global migration, with a focus on crime and housing and rental markets. My recent work examines the New York City migrant housing crisis and small-boat crossings of the English Channel, providing the first econometric evidence on crime rates in these two settings. I am currently researching the intersection of large language models and political economy. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -782,6 +791,13 @@
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -806,9 +822,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1177,7 +1194,7 @@
         <v>129</v>
       </c>
       <c r="I1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1197,7 +1214,7 @@
         <v>131</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1217,13 +1234,13 @@
         <v>131</v>
       </c>
       <c r="F3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1243,7 +1260,7 @@
         <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1263,7 +1280,7 @@
         <v>131</v>
       </c>
       <c r="F5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1283,7 +1300,7 @@
         <v>131</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1303,7 +1320,7 @@
         <v>131</v>
       </c>
       <c r="F7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1320,7 +1337,7 @@
         <v>131</v>
       </c>
       <c r="F8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1340,7 +1357,7 @@
         <v>131</v>
       </c>
       <c r="F9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1360,7 +1377,7 @@
         <v>131</v>
       </c>
       <c r="F10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1380,7 +1397,7 @@
         <v>131</v>
       </c>
       <c r="F11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1400,7 +1417,7 @@
         <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1420,7 +1437,7 @@
         <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1440,7 +1457,7 @@
         <v>131</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1460,7 +1477,7 @@
         <v>131</v>
       </c>
       <c r="F15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1480,27 +1497,27 @@
         <v>131</v>
       </c>
       <c r="F16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" t="s">
         <v>229</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E17" t="s">
         <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1520,7 +1537,7 @@
         <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1534,18 +1551,18 @@
         <v>130</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E19" t="s">
         <v>131</v>
       </c>
       <c r="F19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s">
         <v>32</v>
@@ -1560,7 +1577,7 @@
         <v>131</v>
       </c>
       <c r="F20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1580,7 +1597,7 @@
         <v>131</v>
       </c>
       <c r="F21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1600,7 +1617,7 @@
         <v>131</v>
       </c>
       <c r="F22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1620,7 +1637,7 @@
         <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1640,12 +1657,12 @@
         <v>131</v>
       </c>
       <c r="F24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s">
         <v>136</v>
@@ -1660,18 +1677,27 @@
         <v>131</v>
       </c>
       <c r="F25" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H25" t="s">
+        <v>239</v>
+      </c>
+      <c r="I25" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D26" t="s">
         <v>45</v>
@@ -1680,18 +1706,18 @@
         <v>131</v>
       </c>
       <c r="F26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G26" t="s">
+        <v>232</v>
+      </c>
+      <c r="I26" t="s">
         <v>233</v>
-      </c>
-      <c r="I26" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
@@ -1706,12 +1732,12 @@
         <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
         <v>48</v>
@@ -1726,12 +1752,12 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
         <v>137</v>
@@ -1746,12 +1772,12 @@
         <v>131</v>
       </c>
       <c r="F29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
@@ -1766,12 +1792,12 @@
         <v>131</v>
       </c>
       <c r="F30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
@@ -1786,12 +1812,12 @@
         <v>131</v>
       </c>
       <c r="F31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
         <v>55</v>
@@ -1806,12 +1832,12 @@
         <v>131</v>
       </c>
       <c r="F32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
         <v>57</v>
@@ -1826,12 +1852,12 @@
         <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s">
         <v>60</v>
@@ -1846,21 +1872,21 @@
         <v>131</v>
       </c>
       <c r="F34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
+        <v>235</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" t="s">
         <v>237</v>
-      </c>
-      <c r="I34" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s">
         <v>62</v>
@@ -1872,12 +1898,12 @@
         <v>131</v>
       </c>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
         <v>64</v>
@@ -1892,12 +1918,12 @@
         <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
         <v>66</v>
@@ -1912,12 +1938,12 @@
         <v>131</v>
       </c>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -1946,12 +1972,12 @@
         <v>129</v>
       </c>
       <c r="I40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B41" t="s">
         <v>70</v>
@@ -1963,15 +1989,15 @@
         <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B42" t="s">
         <v>72</v>
@@ -1983,15 +2009,15 @@
         <v>73</v>
       </c>
       <c r="E42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s">
         <v>74</v>
@@ -2003,15 +2029,15 @@
         <v>75</v>
       </c>
       <c r="E43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B44" t="s">
         <v>76</v>
@@ -2023,15 +2049,15 @@
         <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
@@ -2043,15 +2069,15 @@
         <v>79</v>
       </c>
       <c r="E45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B46" t="s">
         <v>80</v>
@@ -2063,15 +2089,15 @@
         <v>81</v>
       </c>
       <c r="E46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B47" t="s">
         <v>82</v>
@@ -2083,15 +2109,15 @@
         <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B48" t="s">
         <v>84</v>
@@ -2103,15 +2129,15 @@
         <v>85</v>
       </c>
       <c r="E48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
         <v>86</v>
@@ -2123,15 +2149,15 @@
         <v>87</v>
       </c>
       <c r="E49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" t="s">
         <v>88</v>
@@ -2143,15 +2169,15 @@
         <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B51" t="s">
         <v>90</v>
@@ -2163,15 +2189,15 @@
         <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
         <v>92</v>
@@ -2183,15 +2209,15 @@
         <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -2220,12 +2246,12 @@
         <v>129</v>
       </c>
       <c r="I55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -2234,18 +2260,18 @@
         <v>130</v>
       </c>
       <c r="D56" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" t="s">
         <v>187</v>
       </c>
-      <c r="E56" t="s">
-        <v>188</v>
-      </c>
       <c r="F56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
@@ -2257,21 +2283,21 @@
         <v>94</v>
       </c>
       <c r="E57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B58" t="s">
         <v>29</v>
@@ -2283,24 +2309,24 @@
         <v>95</v>
       </c>
       <c r="E58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I58" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
@@ -2312,15 +2338,15 @@
         <v>96</v>
       </c>
       <c r="E59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F59" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
@@ -2332,24 +2358,24 @@
         <v>97</v>
       </c>
       <c r="E60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I60" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
@@ -2361,15 +2387,15 @@
         <v>98</v>
       </c>
       <c r="E61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B62" t="s">
         <v>63</v>
@@ -2381,21 +2407,21 @@
         <v>99</v>
       </c>
       <c r="E62" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I62" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B63" t="s">
         <v>68</v>
@@ -2407,15 +2433,15 @@
         <v>100</v>
       </c>
       <c r="E63" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F63" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B64" t="s">
         <v>69</v>
@@ -2427,15 +2453,15 @@
         <v>101</v>
       </c>
       <c r="E64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B65" t="s">
         <v>102</v>
@@ -2447,15 +2473,15 @@
         <v>103</v>
       </c>
       <c r="E65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B66" t="s">
         <v>104</v>
@@ -2467,15 +2493,15 @@
         <v>105</v>
       </c>
       <c r="E66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B67" t="s">
         <v>106</v>
@@ -2484,24 +2510,24 @@
         <v>130</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E67" t="s">
+        <v>187</v>
+      </c>
+      <c r="F67" t="s">
+        <v>171</v>
+      </c>
+      <c r="G67" t="s">
         <v>224</v>
       </c>
-      <c r="E67" t="s">
-        <v>188</v>
-      </c>
-      <c r="F67" t="s">
-        <v>172</v>
-      </c>
-      <c r="G67" t="s">
-        <v>225</v>
-      </c>
       <c r="I67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -2530,12 +2556,12 @@
         <v>129</v>
       </c>
       <c r="I70" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B71" t="s">
         <v>107</v>
@@ -2544,15 +2570,15 @@
         <v>130</v>
       </c>
       <c r="E71" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B72" t="s">
         <v>108</v>
@@ -2564,15 +2590,15 @@
         <v>109</v>
       </c>
       <c r="E72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B73" t="s">
         <v>110</v>
@@ -2584,15 +2610,15 @@
         <v>111</v>
       </c>
       <c r="E73" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B74" t="s">
         <v>112</v>
@@ -2601,15 +2627,15 @@
         <v>130</v>
       </c>
       <c r="E74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F74" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B75" t="s">
         <v>66</v>
@@ -2621,15 +2647,15 @@
         <v>113</v>
       </c>
       <c r="E75" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B76" t="s">
         <v>114</v>
@@ -2641,15 +2667,15 @@
         <v>115</v>
       </c>
       <c r="E76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B77" t="s">
         <v>116</v>
@@ -2661,15 +2687,15 @@
         <v>117</v>
       </c>
       <c r="E77" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B78" t="s">
         <v>118</v>
@@ -2681,15 +2707,15 @@
         <v>119</v>
       </c>
       <c r="E78" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F78" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B79" t="s">
         <v>120</v>
@@ -2701,10 +2727,10 @@
         <v>121</v>
       </c>
       <c r="E79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A00893EE-034A-4A94-BD6D-2EA95DBEE601}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943E18FA-12E9-4995-8460-01FFBAE434D4}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="245">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -762,6 +762,15 @@
   </si>
   <si>
     <t>I am an empirical social scientist studying the effects of global migration, with a focus on crime and housing and rental markets. My recent work examines the New York City migrant housing crisis and small-boat crossings of the English Channel, providing the first econometric evidence on crime rates in these two settings. I am currently researching the intersection of large language models and political economy. </t>
+  </si>
+  <si>
+    <t>https://www.prf.cuni.cz/en/detail-cloveka/808481</t>
+  </si>
+  <si>
+    <t>Pavel Ondřejek is an Associate Professor of Theory, Philosophy and Sociology of Law at the Faculty of Law, Charles University in Prague (Czechia). He has been a research fellow at the Research Centre for Human Rights of Charles University (2012–2023) and at the Systemic Risks Institute (2022–2025). He is the author of a book titled Defragmentation of Law. Reconstruction of Contemporary Law as a System (Cambridge: Intersentia, 2023) as well as numerous articles published in premiere law journals home and abroad, including European Constitutional Law Review, European Public Law and European Journal of Risk Regulation.</t>
+  </si>
+  <si>
+    <t>pavel_ondrejek.png</t>
   </si>
 </sst>
 </file>
@@ -1814,6 +1823,15 @@
       <c r="F31" t="s">
         <v>171</v>
       </c>
+      <c r="G31" t="s">
+        <v>243</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I31" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -2743,6 +2761,7 @@
     <hyperlink ref="D19" r:id="rId6" xr:uid="{F28CF6A1-4168-42B7-9C73-DC7334195F2B}"/>
     <hyperlink ref="D17" r:id="rId7" xr:uid="{24AA546C-6CCE-49CE-9B7B-A5ABBEA6023C}"/>
     <hyperlink ref="H34" r:id="rId8" tooltip="https://sites.google.com/view/msoltes/home" xr:uid="{ED89B3E5-CB58-4B08-937D-91DE2FB52B16}"/>
+    <hyperlink ref="H31" r:id="rId9" tooltip="https://www.prf.cuni.cz/en/detail-cloveka/808481" xr:uid="{22845A3F-D96A-4E87-9454-2C8AC0D1D9FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943E18FA-12E9-4995-8460-01FFBAE434D4}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F125CB5A-73C0-41E1-BBC5-FC8EE3FC3462}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="247">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -771,6 +771,13 @@
   </si>
   <si>
     <t>pavel_ondrejek.png</t>
+  </si>
+  <si>
+    <t>Assistant Professor and Department Coordinator at the Department of Constitutional Law, Faculty of Law of Charles University, and an Analyst at the Office of the President of the Czech Republic. His expertise spans jurisprudence, constitutional theory, and national security law, including emergency governance and control of the armed forces.
+He received the 2023 Praemium excellentiae Dean’s Prize for his outstanding dissertation, which also earned a 2024 honorary mention from the State Security Council. Furthermore, he dedicates his legal skills to the non-profit sector with the Junák – Czech Scout Association.</t>
+  </si>
+  <si>
+    <t>jakub_dienstbier.jpg</t>
   </si>
 </sst>
 </file>
@@ -831,10 +838,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1349,7 +1359,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>145</v>
       </c>
@@ -1367,6 +1377,12 @@
       </c>
       <c r="F9" t="s">
         <v>171</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I9" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F125CB5A-73C0-41E1-BBC5-FC8EE3FC3462}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{655FAC90-BDF9-4ADB-94F1-548F9A3E7464}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="250">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -778,6 +778,15 @@
   </si>
   <si>
     <t>jakub_dienstbier.jpg</t>
+  </si>
+  <si>
+    <t>Libor Dušek is an Associate Professor and Chair of the Department of Economics and Empirical Legal Studies at the Charles University, Faculty of Law in Prague. His research expertise includes Law &amp; Economics, economics of crime, and tax policy. He earned his Master’s in Economics from the Charles University, Faculty of Social Sciences, and his PhD in Economics from the University of Chicago. In his previous positions, he worked at CERGE-EI, IDEA think-tank and the Department of Institutional Economics at the Prague University of Business and Economics. His recent research was published in the Journal of the European Economic Association or the Journal of Quantitative Criminology. He received the “Young Economist of the Year” award from the Czech Economic Society in 2003. Between 2022-2025 served as the member of the National Economic Council of the Government.</t>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/libordusek/home</t>
+  </si>
+  <si>
+    <t>Libor_Dušek.jpg</t>
   </si>
 </sst>
 </file>
@@ -1464,6 +1473,15 @@
       <c r="F13" t="s">
         <v>171</v>
       </c>
+      <c r="G13" t="s">
+        <v>247</v>
+      </c>
+      <c r="H13" t="s">
+        <v>248</v>
+      </c>
+      <c r="I13" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{655FAC90-BDF9-4ADB-94F1-548F9A3E7464}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7934FB-4044-49DF-BE47-CAAAC51175D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="252">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -787,6 +787,12 @@
   </si>
   <si>
     <t>Libor_Dušek.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristina Koldinská is a professor of social security and labour law at the Faculty of Law of Charles University in Prague. Since 1997 she has been working at the Department of Labour Law and Social Security Law. She publishes extensively in the Czech Republic and abroad, in various foreign publishing houses and legal journals. Her research interests include gender equality, discrimination in general, EU social law, social security coordination, social assistance. She is a member of the European Committee of Social Rights. As for expert networks, Kristina is member of the European network of legal experts in gender and non-discrimination and the MoveS network (Free movement and coordination of social security), which are long-term projects led by prestigious European universities and funded by the EU Commission. She is a member of the Legislative Council of the Government of the Czech Republic, the Scientific Council of Charles University, the Scientific Council of the Faculty of Law of Charles University. Since 2026, Kristina is vice-dean for doctoral studies at the same faculty. </t>
+  </si>
+  <si>
+    <t>kristina_koldinska.jpg</t>
   </si>
 </sst>
 </file>
@@ -1702,6 +1708,12 @@
       <c r="F24" t="s">
         <v>171</v>
       </c>
+      <c r="G24" t="s">
+        <v>250</v>
+      </c>
+      <c r="I24" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7934FB-4044-49DF-BE47-CAAAC51175D0}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1743A71B-AB55-46C4-85BB-F01B1249981F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="254">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -793,6 +793,12 @@
   </si>
   <si>
     <t>kristina_koldinska.jpg</t>
+  </si>
+  <si>
+    <t>Devrim Kabasakal Badamchi is a senior researcher at the Institute for the Interregional Study of Constitutionalism at Charles University. Previously, she held research and teaching positions at Leiden University in the Netherlands and SOAS, University of London, in the UK. She was a visiting fellow at Newcastle University and New School University. Her research focuses on the political theory of rights and liberties. Particularly, she is interested in multiculturalism, tolerance, free speech and hate speech. She is also interested in comparative political theory with a focus on constitutionalism and democratic backsliding in Turkey along with digital politics and democratic deliberation.</t>
+  </si>
+  <si>
+    <t>devrim.png</t>
   </si>
 </sst>
 </file>
@@ -1628,6 +1634,12 @@
       <c r="F20" t="s">
         <v>171</v>
       </c>
+      <c r="G20" t="s">
+        <v>252</v>
+      </c>
+      <c r="I20" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -2810,5 +2822,6 @@
     <hyperlink ref="H31" r:id="rId9" tooltip="https://www.prf.cuni.cz/en/detail-cloveka/808481" xr:uid="{22845A3F-D96A-4E87-9454-2C8AC0D1D9FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
 </worksheet>
 </file>
--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1743A71B-AB55-46C4-85BB-F01B1249981F}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3776AA51-5708-4C4E-8318-022C70E367C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="255">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -799,6 +799,9 @@
   </si>
   <si>
     <t>devrim.png</t>
+  </si>
+  <si>
+    <t>Michal Šoltés is an assistant professor at the Department of Economics and Empirical Legal Studies at the Faculty of Law, Charles University, and a researcher at CERGE-EI. His research focuses on the interaction between institutional features of criminal justice systems and the decision-making of individual stakeholders, as well as on public procurement and the effects of family policy on parents’ labor market outcomes. His work has been published in journals, such as the Journal of Public Economics, the Journal of Experimental Criminology, and Labour Economics. He earned his Ph.D. in Economics from CERGE-EI.</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +1954,7 @@
         <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>236</v>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3776AA51-5708-4C4E-8318-022C70E367C6}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137B1D60-0AF9-4A4E-903E-6C5838B9408D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="260">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -519,9 +519,6 @@
   </si>
   <si>
     <t>Alena McClure</t>
-  </si>
-  <si>
-    <t>Karl Nicolas Mittag</t>
   </si>
   <si>
     <t>Josef Montag</t>
@@ -802,13 +799,31 @@
   </si>
   <si>
     <t>Michal Šoltés is an assistant professor at the Department of Economics and Empirical Legal Studies at the Faculty of Law, Charles University, and a researcher at CERGE-EI. His research focuses on the interaction between institutional features of criminal justice systems and the decision-making of individual stakeholders, as well as on public procurement and the effects of family policy on parents’ labor market outcomes. His work has been published in journals, such as the Journal of Public Economics, the Journal of Experimental Criminology, and Labour Economics. He earned his Ph.D. in Economics from CERGE-EI.</t>
+  </si>
+  <si>
+    <t>Nikolas Mittag</t>
+  </si>
+  <si>
+    <t>My work sits at the intersection of applied econometrics, program evaluation, public economics and labor economics, with particular expertise in measurement error and the use of linked survey–administrative data to improve official statistics and program evaluation. My research has been published in journals such as the Journal of Econometrics, AEJ: Applied Economics, the Quarterly Journal of Political Science and the Review of Economics and Statistics; recent projects include studies on survey error decomposition and measurement of income and program participation. </t>
+  </si>
+  <si>
+    <t>https://home.cerge-ei.cz/mittag/</t>
+  </si>
+  <si>
+    <t>mittag.jpg</t>
+  </si>
+  <si>
+    <t>Prof. Veronika Bílková is Head of the Department of International Law at the Faculty of Law of Charles University and Head of the University Centre for Conflict and Post-Conflict Studies. She is also a senior research fellow at the Centre for International Law at the Institute of International Relations in Prague. She is a member of the Venice Commission of the Council of Europe (since 2010) and a member of the COMEX (since 2025). She has participated in five expert missions on Ukraine established under the so-called OSCE Moscow Mechanism (2022-2025). Her research areas include the use of force, international humanitarian law, international human rights law, international criminal law and counter-terrorism. She has published widely in Czech, English and French.</t>
+  </si>
+  <si>
+    <t>veronika_bilkova.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -839,6 +854,12 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -862,13 +883,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1237,7 +1259,7 @@
         <v>129</v>
       </c>
       <c r="I1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1257,7 +1279,7 @@
         <v>131</v>
       </c>
       <c r="F2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1277,13 +1299,13 @@
         <v>131</v>
       </c>
       <c r="F3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1303,7 +1325,7 @@
         <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1323,10 +1345,10 @@
         <v>131</v>
       </c>
       <c r="F5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1343,7 +1365,13 @@
         <v>131</v>
       </c>
       <c r="F6" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="I6" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1363,7 +1391,7 @@
         <v>131</v>
       </c>
       <c r="F7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1380,7 +1408,7 @@
         <v>131</v>
       </c>
       <c r="F8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1400,13 +1428,13 @@
         <v>131</v>
       </c>
       <c r="F9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I9" t="s">
         <v>245</v>
-      </c>
-      <c r="I9" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1426,7 +1454,7 @@
         <v>131</v>
       </c>
       <c r="F10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1446,7 +1474,7 @@
         <v>131</v>
       </c>
       <c r="F11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1466,7 +1494,7 @@
         <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1486,16 +1514,16 @@
         <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G13" t="s">
+        <v>246</v>
+      </c>
+      <c r="H13" t="s">
         <v>247</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>248</v>
-      </c>
-      <c r="I13" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1515,7 +1543,7 @@
         <v>131</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1535,7 +1563,7 @@
         <v>131</v>
       </c>
       <c r="F15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1555,27 +1583,27 @@
         <v>131</v>
       </c>
       <c r="F16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" t="s">
         <v>228</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E17" t="s">
         <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1595,7 +1623,7 @@
         <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1609,18 +1637,18 @@
         <v>130</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" t="s">
         <v>131</v>
       </c>
       <c r="F19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
         <v>32</v>
@@ -1635,13 +1663,13 @@
         <v>131</v>
       </c>
       <c r="F20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G20" t="s">
+        <v>251</v>
+      </c>
+      <c r="I20" t="s">
         <v>252</v>
-      </c>
-      <c r="I20" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1661,7 +1689,7 @@
         <v>131</v>
       </c>
       <c r="F21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1681,7 +1709,7 @@
         <v>131</v>
       </c>
       <c r="F22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1701,7 +1729,7 @@
         <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1721,18 +1749,18 @@
         <v>131</v>
       </c>
       <c r="F24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G24" t="s">
+        <v>249</v>
+      </c>
+      <c r="I24" t="s">
         <v>250</v>
-      </c>
-      <c r="I24" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s">
         <v>136</v>
@@ -1747,16 +1775,16 @@
         <v>131</v>
       </c>
       <c r="F25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H25" t="s">
+        <v>238</v>
+      </c>
+      <c r="I25" t="s">
         <v>239</v>
-      </c>
-      <c r="I25" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -1767,7 +1795,7 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s">
         <v>45</v>
@@ -1776,13 +1804,13 @@
         <v>131</v>
       </c>
       <c r="F26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G26" t="s">
+        <v>231</v>
+      </c>
+      <c r="I26" t="s">
         <v>232</v>
-      </c>
-      <c r="I26" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -1802,12 +1830,12 @@
         <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s">
         <v>48</v>
@@ -1822,12 +1850,21 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="G28" t="s">
+        <v>255</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I28" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s">
         <v>137</v>
@@ -1842,12 +1879,12 @@
         <v>131</v>
       </c>
       <c r="F29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
@@ -1862,12 +1899,12 @@
         <v>131</v>
       </c>
       <c r="F30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
@@ -1882,21 +1919,21 @@
         <v>131</v>
       </c>
       <c r="F31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G31" t="s">
+        <v>242</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I31" t="s">
         <v>243</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I31" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s">
         <v>55</v>
@@ -1911,12 +1948,12 @@
         <v>131</v>
       </c>
       <c r="F32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
         <v>57</v>
@@ -1931,12 +1968,12 @@
         <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
         <v>60</v>
@@ -1951,21 +1988,21 @@
         <v>131</v>
       </c>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I34" t="s">
         <v>236</v>
-      </c>
-      <c r="I34" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
         <v>62</v>
@@ -1977,12 +2014,12 @@
         <v>131</v>
       </c>
       <c r="F35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
         <v>64</v>
@@ -1997,12 +2034,12 @@
         <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
         <v>66</v>
@@ -2017,12 +2054,12 @@
         <v>131</v>
       </c>
       <c r="F37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -2051,12 +2088,12 @@
         <v>129</v>
       </c>
       <c r="I40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B41" t="s">
         <v>70</v>
@@ -2068,15 +2105,15 @@
         <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B42" t="s">
         <v>72</v>
@@ -2088,15 +2125,15 @@
         <v>73</v>
       </c>
       <c r="E42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B43" t="s">
         <v>74</v>
@@ -2108,15 +2145,15 @@
         <v>75</v>
       </c>
       <c r="E43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B44" t="s">
         <v>76</v>
@@ -2128,15 +2165,15 @@
         <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
@@ -2148,15 +2185,15 @@
         <v>79</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
         <v>80</v>
@@ -2168,15 +2205,15 @@
         <v>81</v>
       </c>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B47" t="s">
         <v>82</v>
@@ -2188,15 +2225,15 @@
         <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" t="s">
         <v>84</v>
@@ -2208,15 +2245,15 @@
         <v>85</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" t="s">
         <v>86</v>
@@ -2228,15 +2265,15 @@
         <v>87</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B50" t="s">
         <v>88</v>
@@ -2248,15 +2285,15 @@
         <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B51" t="s">
         <v>90</v>
@@ -2268,15 +2305,15 @@
         <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B52" t="s">
         <v>92</v>
@@ -2288,15 +2325,15 @@
         <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -2325,12 +2362,12 @@
         <v>129</v>
       </c>
       <c r="I55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -2339,18 +2376,18 @@
         <v>130</v>
       </c>
       <c r="D56" t="s">
+        <v>185</v>
+      </c>
+      <c r="E56" t="s">
         <v>186</v>
       </c>
-      <c r="E56" t="s">
-        <v>187</v>
-      </c>
       <c r="F56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
@@ -2362,21 +2399,21 @@
         <v>94</v>
       </c>
       <c r="E57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H57" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
         <v>29</v>
@@ -2388,24 +2425,24 @@
         <v>95</v>
       </c>
       <c r="E58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F58" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G58" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
@@ -2417,15 +2454,15 @@
         <v>96</v>
       </c>
       <c r="E59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F59" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
@@ -2437,24 +2474,24 @@
         <v>97</v>
       </c>
       <c r="E60" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G60" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I60" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
@@ -2466,15 +2503,15 @@
         <v>98</v>
       </c>
       <c r="E61" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F61" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B62" t="s">
         <v>63</v>
@@ -2486,21 +2523,21 @@
         <v>99</v>
       </c>
       <c r="E62" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F62" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I62" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B63" t="s">
         <v>68</v>
@@ -2512,15 +2549,15 @@
         <v>100</v>
       </c>
       <c r="E63" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F63" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B64" t="s">
         <v>69</v>
@@ -2532,15 +2569,15 @@
         <v>101</v>
       </c>
       <c r="E64" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B65" t="s">
         <v>102</v>
@@ -2552,15 +2589,15 @@
         <v>103</v>
       </c>
       <c r="E65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B66" t="s">
         <v>104</v>
@@ -2572,15 +2609,15 @@
         <v>105</v>
       </c>
       <c r="E66" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F66" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B67" t="s">
         <v>106</v>
@@ -2589,24 +2626,24 @@
         <v>130</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E67" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" t="s">
+        <v>170</v>
+      </c>
+      <c r="G67" t="s">
         <v>223</v>
       </c>
-      <c r="E67" t="s">
-        <v>187</v>
-      </c>
-      <c r="F67" t="s">
-        <v>171</v>
-      </c>
-      <c r="G67" t="s">
-        <v>224</v>
-      </c>
       <c r="I67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -2635,12 +2672,12 @@
         <v>129</v>
       </c>
       <c r="I70" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B71" t="s">
         <v>107</v>
@@ -2649,15 +2686,15 @@
         <v>130</v>
       </c>
       <c r="E71" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B72" t="s">
         <v>108</v>
@@ -2669,15 +2706,15 @@
         <v>109</v>
       </c>
       <c r="E72" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B73" t="s">
         <v>110</v>
@@ -2689,15 +2726,15 @@
         <v>111</v>
       </c>
       <c r="E73" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B74" t="s">
         <v>112</v>
@@ -2706,15 +2743,15 @@
         <v>130</v>
       </c>
       <c r="E74" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B75" t="s">
         <v>66</v>
@@ -2726,15 +2763,15 @@
         <v>113</v>
       </c>
       <c r="E75" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B76" t="s">
         <v>114</v>
@@ -2746,15 +2783,15 @@
         <v>115</v>
       </c>
       <c r="E76" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B77" t="s">
         <v>116</v>
@@ -2766,15 +2803,15 @@
         <v>117</v>
       </c>
       <c r="E77" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F77" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B78" t="s">
         <v>118</v>
@@ -2786,15 +2823,15 @@
         <v>119</v>
       </c>
       <c r="E78" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F78" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B79" t="s">
         <v>120</v>
@@ -2806,10 +2843,10 @@
         <v>121</v>
       </c>
       <c r="E79" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2823,8 +2860,9 @@
     <hyperlink ref="D17" r:id="rId7" xr:uid="{24AA546C-6CCE-49CE-9B7B-A5ABBEA6023C}"/>
     <hyperlink ref="H34" r:id="rId8" tooltip="https://sites.google.com/view/msoltes/home" xr:uid="{ED89B3E5-CB58-4B08-937D-91DE2FB52B16}"/>
     <hyperlink ref="H31" r:id="rId9" tooltip="https://www.prf.cuni.cz/en/detail-cloveka/808481" xr:uid="{22845A3F-D96A-4E87-9454-2C8AC0D1D9FC}"/>
+    <hyperlink ref="H28" r:id="rId10" tooltip="https://home.cerge-ei.cz/mittag/" xr:uid="{A0AE1B7A-7E12-4897-A483-A54318E90ABE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId11"/>
 </worksheet>
 </file>
--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137B1D60-0AF9-4A4E-903E-6C5838B9408D}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{594A8394-05FE-4A64-B567-C2FDABAE9942}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="280">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -817,13 +817,73 @@
   </si>
   <si>
     <t>veronika_bilkova.jpg</t>
+  </si>
+  <si>
+    <t>Will Bennis’s research focuses on how culture, the built environment, and cognition shape normative judgments (judgments about what is rational, adaptive, true, or moral) and examines the extent to which those judgments, and the decisions they inform, can themselves be considered normative.</t>
+  </si>
+  <si>
+    <t>Will_Bennis.jpg</t>
+  </si>
+  <si>
+    <t>Claire_Mollier.jpg</t>
+  </si>
+  <si>
+    <t>Peter_Preglej.jpg</t>
+  </si>
+  <si>
+    <t>Petr_Houdek.jpg</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=GsLe4O8AAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://clairemollier.weebly.com/</t>
+  </si>
+  <si>
+    <t>Claire Mollier’s research focuses on gender, discrimination, and inequality, using both lab and field experiments. She also values science communication by sharing her work through (French) YouTube videos for instance. She founded and organized during 2 years informal research seminars in Paris with junior experimentalists.</t>
+  </si>
+  <si>
+    <t>Klara_Urbanova.jpg</t>
+  </si>
+  <si>
+    <t>Klára Urbanová is interested in how behavioral economics can explain and improve decision-making in communication (both commercial and institutional), including nudging and gamification. Her current research explores anchoring bias in promotional contexts. She holds both academic and professional experience in international business and marcom.</t>
+  </si>
+  <si>
+    <t>Lenka_Valerianova.jpg</t>
+  </si>
+  <si>
+    <t>Lenka Valerianová is interested in behavioral economics (especially behavioral finance) in the contrext of topics such as decision making, deception, fraud and crime. Her current research uses experimental methods to study willingness (and ability) to deceive.</t>
+  </si>
+  <si>
+    <t>Stepan_Bahnik.jpg</t>
+  </si>
+  <si>
+    <t>Štěpán Bahník’s research focuses on judgment and decision-making, with particular emphasis on moral judgment and behavior, the anchoring effect, and processing fluency. He is also interested in open science, psychological methodology, statistics, programming, and the intersections between psychology and computer science.</t>
+  </si>
+  <si>
+    <t>https://bahniks.com/</t>
+  </si>
+  <si>
+    <t>Petr Houdek specializes in behavioral economics, focusing on how people perceive information, reason, and make decisions, not only in economic contexts. He works on improving employee and managerial decision-making through choice architecture (nudging) in organizations and the public sector. He also conducts field and laboratory experiments on dishonesty and decision-making biases.</t>
+  </si>
+  <si>
+    <t>https://houdekpetr.blogspot.com/</t>
+  </si>
+  <si>
+    <t>Alessandro.jpg</t>
+  </si>
+  <si>
+    <t>Alessandro Stringhi’s research focuses on prosocial behavior, with a particular emphasis on understanding and mitigating the social and behavioral consequences of inequality. He has a growing interest in the economic and institutional roots of organized crime, using field and lab experiments to study how social norms and collective behavior respond to corruption and criminal infiltration. His approach combines experimental methods with formal tools from game theory, aiming to build structurally grounded explanations for complex social and moral behavior.</t>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/alessandrostringhi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,6 +920,13 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -883,7 +950,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -891,6 +958,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2691,6 +2759,15 @@
       <c r="F71" t="s">
         <v>170</v>
       </c>
+      <c r="G71" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="H71" t="s">
+        <v>265</v>
+      </c>
+      <c r="I71" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -2711,6 +2788,15 @@
       <c r="F72" t="s">
         <v>170</v>
       </c>
+      <c r="G72" t="s">
+        <v>267</v>
+      </c>
+      <c r="H72" t="s">
+        <v>266</v>
+      </c>
+      <c r="I72" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -2731,6 +2817,9 @@
       <c r="F73" t="s">
         <v>170</v>
       </c>
+      <c r="I73" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -2768,6 +2857,12 @@
       <c r="F75" t="s">
         <v>170</v>
       </c>
+      <c r="G75" t="s">
+        <v>269</v>
+      </c>
+      <c r="I75" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -2788,6 +2883,12 @@
       <c r="F76" t="s">
         <v>170</v>
       </c>
+      <c r="G76" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="I76" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -2808,6 +2909,15 @@
       <c r="F77" t="s">
         <v>170</v>
       </c>
+      <c r="G77" t="s">
+        <v>273</v>
+      </c>
+      <c r="H77" t="s">
+        <v>274</v>
+      </c>
+      <c r="I77" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -2828,6 +2938,15 @@
       <c r="F78" t="s">
         <v>170</v>
       </c>
+      <c r="G78" t="s">
+        <v>275</v>
+      </c>
+      <c r="H78" t="s">
+        <v>276</v>
+      </c>
+      <c r="I78" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -2847,6 +2966,15 @@
       </c>
       <c r="F79" t="s">
         <v>170</v>
+      </c>
+      <c r="G79" t="s">
+        <v>278</v>
+      </c>
+      <c r="H79" t="s">
+        <v>279</v>
+      </c>
+      <c r="I79" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{594A8394-05FE-4A64-B567-C2FDABAE9942}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{765304E1-C4EB-449A-B28E-AC4AC8BD7167}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="283">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -339,9 +339,6 @@
   </si>
   <si>
     <t>tereza.vesela@fsv.cuni.cz</t>
-  </si>
-  <si>
-    <t>29619066@o365.cuni.cz</t>
   </si>
   <si>
     <t>Baxa</t>
@@ -877,13 +874,45 @@
   </si>
   <si>
     <t>https://sites.google.com/view/alessandrostringhi</t>
+  </si>
+  <si>
+    <t>laurent.weill@unistra.fr</t>
+  </si>
+  <si>
+    <r>
+      <t>Laurent Weill works on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t>banking, corporate finance and political economy.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t> He has published more than 150 papers including 140 papers in peer-reviewed journals, among others Journal of Comparative Economics, World Development, Public Choice, Journal of Banking and Finance, and Journal of Financial Stability.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://sites.google.com/site/laurentweillstrasbourg/home</t>
+  </si>
+  <si>
+    <t>Laurent.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -927,6 +956,18 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -950,7 +991,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -959,6 +1000,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1296,1685 +1338,1694 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE358DA8-D777-4377-96EA-27F7BC555635}">
   <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" t="s">
         <v>122</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>123</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>124</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>125</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>126</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>127</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>128</v>
       </c>
-      <c r="H1" t="s">
-        <v>129</v>
-      </c>
       <c r="I1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s">
         <v>131</v>
       </c>
-      <c r="F3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G3" t="s">
-        <v>234</v>
-      </c>
-      <c r="I3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" t="s">
-        <v>132</v>
-      </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.6">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I6" t="s">
         <v>258</v>
       </c>
-      <c r="I6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="13.2" customHeight="1">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I9" t="s">
         <v>244</v>
       </c>
-      <c r="I9" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F12" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G13" t="s">
+        <v>245</v>
+      </c>
+      <c r="H13" t="s">
         <v>246</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>247</v>
       </c>
-      <c r="I13" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F14" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F16" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" t="s">
         <v>227</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F17" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s">
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
         <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I20" t="s">
         <v>251</v>
       </c>
-      <c r="I20" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
         <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
         <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B23" t="s">
         <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G24" t="s">
+        <v>248</v>
+      </c>
+      <c r="I24" t="s">
         <v>249</v>
       </c>
-      <c r="I24" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
         <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H25" t="s">
+        <v>237</v>
+      </c>
+      <c r="I25" t="s">
         <v>238</v>
       </c>
-      <c r="I25" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D26" t="s">
         <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G26" t="s">
+        <v>230</v>
+      </c>
+      <c r="I26" t="s">
         <v>231</v>
       </c>
-      <c r="I26" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s">
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G28" t="s">
+        <v>254</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" t="s">
         <v>256</v>
       </c>
-      <c r="I28" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
         <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
         <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
         <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G31" t="s">
+        <v>241</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I31" t="s">
         <v>242</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I31" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B32" t="s">
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
         <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
         <v>57</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
         <v>58</v>
       </c>
       <c r="E33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
         <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
         <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I34" t="s">
         <v>235</v>
       </c>
-      <c r="I34" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
         <v>62</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F35" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
         <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
         <v>65</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
         <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F37" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
         <v>122</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>123</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>124</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>125</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>126</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>127</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>128</v>
       </c>
-      <c r="H40" t="s">
-        <v>129</v>
-      </c>
       <c r="I40" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s">
         <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D41" t="s">
         <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F41" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s">
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
         <v>73</v>
       </c>
       <c r="E42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
         <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D43" t="s">
         <v>75</v>
       </c>
       <c r="E43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F43" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B44" t="s">
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D44" t="s">
         <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F44" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D45" t="s">
         <v>79</v>
       </c>
       <c r="E45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F45" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B46" t="s">
         <v>80</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
         <v>81</v>
       </c>
       <c r="E46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F46" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
         <v>82</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D47" t="s">
         <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" t="s">
         <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D48" t="s">
         <v>85</v>
       </c>
       <c r="E48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" t="s">
         <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D49" t="s">
         <v>87</v>
       </c>
       <c r="E49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F49" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B50" t="s">
         <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D50" t="s">
         <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F50" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B51" t="s">
         <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D51" t="s">
         <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F51" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
         <v>92</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D52" t="s">
         <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F52" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" t="s">
         <v>122</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>123</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>124</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>125</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>126</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>127</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>128</v>
       </c>
-      <c r="H55" t="s">
-        <v>129</v>
-      </c>
       <c r="I55" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D56" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" t="s">
         <v>185</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
         <v>186</v>
-      </c>
-      <c r="F56" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>187</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D57" t="s">
         <v>94</v>
       </c>
       <c r="E57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s">
         <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D58" t="s">
         <v>95</v>
       </c>
       <c r="E58" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G58" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I58" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
       </c>
       <c r="E59" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F59" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
       </c>
       <c r="C60" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D60" t="s">
         <v>97</v>
       </c>
       <c r="E60" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I60" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D61" t="s">
         <v>98</v>
       </c>
       <c r="E61" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F61" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B62" t="s">
         <v>63</v>
       </c>
       <c r="C62" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D62" t="s">
         <v>99</v>
       </c>
       <c r="E62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I62" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B63" t="s">
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D63" t="s">
         <v>100</v>
       </c>
       <c r="E63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F63" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B64" t="s">
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" t="s">
+        <v>129</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E64" t="s">
+        <v>185</v>
+      </c>
+      <c r="F64" t="s">
+        <v>169</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I64" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
         <v>101</v>
       </c>
-      <c r="E64" t="s">
-        <v>186</v>
-      </c>
-      <c r="F64" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="C65" t="s">
+        <v>129</v>
+      </c>
+      <c r="D65" t="s">
+        <v>102</v>
+      </c>
+      <c r="E65" t="s">
+        <v>185</v>
+      </c>
+      <c r="F65" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
         <v>195</v>
       </c>
-      <c r="B65" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="B66" t="s">
         <v>103</v>
       </c>
-      <c r="E65" t="s">
-        <v>186</v>
-      </c>
-      <c r="F65" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="C66" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" t="s">
+        <v>104</v>
+      </c>
+      <c r="E66" t="s">
+        <v>185</v>
+      </c>
+      <c r="F66" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
         <v>196</v>
       </c>
-      <c r="B66" t="s">
-        <v>104</v>
-      </c>
-      <c r="C66" t="s">
-        <v>130</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="B67" t="s">
         <v>105</v>
       </c>
-      <c r="E66" t="s">
-        <v>186</v>
-      </c>
-      <c r="F66" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="C67" t="s">
+        <v>129</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E67" t="s">
+        <v>185</v>
+      </c>
+      <c r="F67" t="s">
+        <v>169</v>
+      </c>
+      <c r="G67" t="s">
+        <v>222</v>
+      </c>
+      <c r="I67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" t="s">
+        <v>122</v>
+      </c>
+      <c r="C70" t="s">
+        <v>123</v>
+      </c>
+      <c r="D70" t="s">
+        <v>124</v>
+      </c>
+      <c r="E70" t="s">
+        <v>125</v>
+      </c>
+      <c r="F70" t="s">
+        <v>126</v>
+      </c>
+      <c r="G70" t="s">
+        <v>127</v>
+      </c>
+      <c r="H70" t="s">
+        <v>128</v>
+      </c>
+      <c r="I70" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
         <v>197</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B71" t="s">
         <v>106</v>
       </c>
-      <c r="C67" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E67" t="s">
-        <v>186</v>
-      </c>
-      <c r="F67" t="s">
-        <v>170</v>
-      </c>
-      <c r="G67" t="s">
-        <v>223</v>
-      </c>
-      <c r="I67" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>122</v>
-      </c>
-      <c r="B70" t="s">
-        <v>123</v>
-      </c>
-      <c r="C70" t="s">
-        <v>124</v>
-      </c>
-      <c r="D70" t="s">
-        <v>125</v>
-      </c>
-      <c r="E70" t="s">
-        <v>126</v>
-      </c>
-      <c r="F70" t="s">
-        <v>127</v>
-      </c>
-      <c r="G70" t="s">
-        <v>128</v>
-      </c>
-      <c r="H70" t="s">
-        <v>129</v>
-      </c>
-      <c r="I70" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="C71" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" t="s">
         <v>198</v>
       </c>
-      <c r="B71" t="s">
+      <c r="F71" t="s">
+        <v>169</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H71" t="s">
+        <v>264</v>
+      </c>
+      <c r="I71" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" t="s">
         <v>107</v>
       </c>
-      <c r="C71" t="s">
-        <v>130</v>
-      </c>
-      <c r="E71" t="s">
-        <v>199</v>
-      </c>
-      <c r="F71" t="s">
-        <v>170</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="H71" t="s">
+      <c r="C72" t="s">
+        <v>129</v>
+      </c>
+      <c r="D72" t="s">
+        <v>108</v>
+      </c>
+      <c r="E72" t="s">
+        <v>198</v>
+      </c>
+      <c r="F72" t="s">
+        <v>169</v>
+      </c>
+      <c r="G72" t="s">
+        <v>266</v>
+      </c>
+      <c r="H72" t="s">
         <v>265</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I72" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
         <v>200</v>
       </c>
-      <c r="B72" t="s">
-        <v>108</v>
-      </c>
-      <c r="C72" t="s">
-        <v>130</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="B73" t="s">
         <v>109</v>
       </c>
-      <c r="E72" t="s">
-        <v>199</v>
-      </c>
-      <c r="F72" t="s">
-        <v>170</v>
-      </c>
-      <c r="G72" t="s">
-        <v>267</v>
-      </c>
-      <c r="H72" t="s">
-        <v>266</v>
-      </c>
-      <c r="I72" t="s">
+      <c r="C73" t="s">
+        <v>129</v>
+      </c>
+      <c r="D73" t="s">
+        <v>110</v>
+      </c>
+      <c r="E73" t="s">
+        <v>198</v>
+      </c>
+      <c r="F73" t="s">
+        <v>169</v>
+      </c>
+      <c r="I73" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
         <v>201</v>
       </c>
-      <c r="B73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C73" t="s">
-        <v>130</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="B74" t="s">
         <v>111</v>
       </c>
-      <c r="E73" t="s">
-        <v>199</v>
-      </c>
-      <c r="F73" t="s">
-        <v>170</v>
-      </c>
-      <c r="I73" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="C74" t="s">
+        <v>129</v>
+      </c>
+      <c r="E74" t="s">
+        <v>198</v>
+      </c>
+      <c r="F74" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
         <v>202</v>
-      </c>
-      <c r="B74" t="s">
-        <v>112</v>
-      </c>
-      <c r="C74" t="s">
-        <v>130</v>
-      </c>
-      <c r="E74" t="s">
-        <v>199</v>
-      </c>
-      <c r="F74" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>203</v>
       </c>
       <c r="B75" t="s">
         <v>66</v>
       </c>
       <c r="C75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D75" t="s">
+        <v>112</v>
+      </c>
+      <c r="E75" t="s">
+        <v>198</v>
+      </c>
+      <c r="F75" t="s">
+        <v>169</v>
+      </c>
+      <c r="G75" t="s">
+        <v>268</v>
+      </c>
+      <c r="I75" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>203</v>
+      </c>
+      <c r="B76" t="s">
         <v>113</v>
       </c>
-      <c r="E75" t="s">
-        <v>199</v>
-      </c>
-      <c r="F75" t="s">
-        <v>170</v>
-      </c>
-      <c r="G75" t="s">
+      <c r="C76" t="s">
+        <v>129</v>
+      </c>
+      <c r="D76" t="s">
+        <v>114</v>
+      </c>
+      <c r="E76" t="s">
+        <v>198</v>
+      </c>
+      <c r="F76" t="s">
+        <v>169</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="I76" t="s">
         <v>269</v>
       </c>
-      <c r="I75" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
         <v>204</v>
       </c>
-      <c r="B76" t="s">
-        <v>114</v>
-      </c>
-      <c r="C76" t="s">
-        <v>130</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="B77" t="s">
         <v>115</v>
       </c>
-      <c r="E76" t="s">
-        <v>199</v>
-      </c>
-      <c r="F76" t="s">
-        <v>170</v>
-      </c>
-      <c r="G76" s="5" t="s">
+      <c r="C77" t="s">
+        <v>129</v>
+      </c>
+      <c r="D77" t="s">
+        <v>116</v>
+      </c>
+      <c r="E77" t="s">
+        <v>198</v>
+      </c>
+      <c r="F77" t="s">
+        <v>169</v>
+      </c>
+      <c r="G77" t="s">
+        <v>272</v>
+      </c>
+      <c r="H77" t="s">
+        <v>273</v>
+      </c>
+      <c r="I77" t="s">
         <v>271</v>
       </c>
-      <c r="I76" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
         <v>205</v>
       </c>
-      <c r="B77" t="s">
-        <v>116</v>
-      </c>
-      <c r="C77" t="s">
-        <v>130</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="B78" t="s">
         <v>117</v>
       </c>
-      <c r="E77" t="s">
-        <v>199</v>
-      </c>
-      <c r="F77" t="s">
-        <v>170</v>
-      </c>
-      <c r="G77" t="s">
-        <v>273</v>
-      </c>
-      <c r="H77" t="s">
+      <c r="C78" t="s">
+        <v>129</v>
+      </c>
+      <c r="D78" t="s">
+        <v>118</v>
+      </c>
+      <c r="E78" t="s">
+        <v>198</v>
+      </c>
+      <c r="F78" t="s">
+        <v>169</v>
+      </c>
+      <c r="G78" t="s">
         <v>274</v>
       </c>
-      <c r="I77" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="H78" t="s">
+        <v>275</v>
+      </c>
+      <c r="I78" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
         <v>206</v>
       </c>
-      <c r="B78" t="s">
-        <v>118</v>
-      </c>
-      <c r="C78" t="s">
-        <v>130</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="B79" t="s">
         <v>119</v>
       </c>
-      <c r="E78" t="s">
-        <v>199</v>
-      </c>
-      <c r="F78" t="s">
-        <v>170</v>
-      </c>
-      <c r="G78" t="s">
-        <v>275</v>
-      </c>
-      <c r="H78" t="s">
+      <c r="C79" t="s">
+        <v>129</v>
+      </c>
+      <c r="D79" t="s">
+        <v>120</v>
+      </c>
+      <c r="E79" t="s">
+        <v>198</v>
+      </c>
+      <c r="F79" t="s">
+        <v>169</v>
+      </c>
+      <c r="G79" t="s">
+        <v>277</v>
+      </c>
+      <c r="H79" t="s">
+        <v>278</v>
+      </c>
+      <c r="I79" t="s">
         <v>276</v>
-      </c>
-      <c r="I78" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>207</v>
-      </c>
-      <c r="B79" t="s">
-        <v>120</v>
-      </c>
-      <c r="C79" t="s">
-        <v>130</v>
-      </c>
-      <c r="D79" t="s">
-        <v>121</v>
-      </c>
-      <c r="E79" t="s">
-        <v>199</v>
-      </c>
-      <c r="F79" t="s">
-        <v>170</v>
-      </c>
-      <c r="G79" t="s">
-        <v>278</v>
-      </c>
-      <c r="H79" t="s">
-        <v>279</v>
-      </c>
-      <c r="I79" t="s">
-        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -2989,8 +3040,10 @@
     <hyperlink ref="H34" r:id="rId8" tooltip="https://sites.google.com/view/msoltes/home" xr:uid="{ED89B3E5-CB58-4B08-937D-91DE2FB52B16}"/>
     <hyperlink ref="H31" r:id="rId9" tooltip="https://www.prf.cuni.cz/en/detail-cloveka/808481" xr:uid="{22845A3F-D96A-4E87-9454-2C8AC0D1D9FC}"/>
     <hyperlink ref="H28" r:id="rId10" tooltip="https://home.cerge-ei.cz/mittag/" xr:uid="{A0AE1B7A-7E12-4897-A483-A54318E90ABE}"/>
+    <hyperlink ref="D64" r:id="rId11" tooltip="mailto:laurent.weill@unistra.fr" display="mailto:laurent.weill@unistra.fr" xr:uid="{C04E6286-39F3-41C0-84AF-3F9E019F1780}"/>
+    <hyperlink ref="H64" r:id="rId12" tooltip="https://sites.google.com/site/laurentweillstrasbourg/home" xr:uid="{C03A4B72-D83E-424B-A875-03CA43C73FAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
 </worksheet>
 </file>
--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{765304E1-C4EB-449A-B28E-AC4AC8BD7167}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E12E90-F9C4-4CA5-AE8C-3AAE6EAEF785}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="286">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -907,12 +907,80 @@
   <si>
     <t>Laurent.png</t>
   </si>
+  <si>
+    <r>
+      <t>I am a Senior Researcher and Lecturer at Charles University’s Faculty of Law, specializing in legal philosophy, constitutional theory, and comparative legal philosophy. My work integrates Aristotelian, phenomenological, and cross-cultural approaches to justice, rights, and normativity. Previously, I held a Marie Skłodowska-Curie Global Fellowship at Harvard and Ca’ Foscari, leading an EU-funded project on Aristotelian and Neo-Confucian foundations of human rights. I am the author of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Self-Determination Beyond Liberal Legalism: Ethics, Law and the Politics of Justice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t> (Bloomsbury, 2025) and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Aristotle and the Foundations of Rights:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>From Passion to Reason</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t> (Edward Elgar, forthcoming 2026). Before academia, I worked as a senior human rights lawyer for the Greek National Commission for Human Rights.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://annairenebaka.com/</t>
+  </si>
+  <si>
+    <t>anna_baka.webp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,6 +1036,19 @@
       <family val="1"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -991,7 +1072,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1001,6 +1082,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1437,6 +1519,15 @@
       <c r="F4" t="s">
         <v>169</v>
       </c>
+      <c r="G4" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I4" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
@@ -3042,8 +3133,9 @@
     <hyperlink ref="H28" r:id="rId10" tooltip="https://home.cerge-ei.cz/mittag/" xr:uid="{A0AE1B7A-7E12-4897-A483-A54318E90ABE}"/>
     <hyperlink ref="D64" r:id="rId11" tooltip="mailto:laurent.weill@unistra.fr" display="mailto:laurent.weill@unistra.fr" xr:uid="{C04E6286-39F3-41C0-84AF-3F9E019F1780}"/>
     <hyperlink ref="H64" r:id="rId12" tooltip="https://sites.google.com/site/laurentweillstrasbourg/home" xr:uid="{C03A4B72-D83E-424B-A875-03CA43C73FAB}"/>
+    <hyperlink ref="H4" r:id="rId13" tooltip="https://annairenebaka.com/" xr:uid="{CD375092-C532-49C6-AC57-E1CCBA77229B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId14"/>
 </worksheet>
 </file>
--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E12E90-F9C4-4CA5-AE8C-3AAE6EAEF785}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E6F281-CE47-4CBE-8E30-3FD1B12277EF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="290">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -974,6 +974,18 @@
   </si>
   <si>
     <t>anna_baka.webp</t>
+  </si>
+  <si>
+    <t>Dana Ondrejová is an associate professor at the Department of Commercial Law, Faculty of Law, Masaryk University, and an attorney at law. She specialises in unfair competition law, competition law, unfair commercial practices, advertising law, and related aspects of private and market regulation. Her work brings together academic research and legal practice, and she has published extensively in the fields of commercial and competition law. In addition to her academic and professional activities, she serves as an arbitrator, a member of the appellate commission of the Office for the Protection of Competition, a member of the appellate commission of the Energy Regulatory Office in matters concerning consumer protection, and an examiner in commercial law for the Czech Bar Association.</t>
+  </si>
+  <si>
+    <t>JUDr. Michala Špačková, Ph.D., is an Assistant Professor at the Department of Business Law, Faculty of Law, Masaryk University, with an academic background in both law and sociology. Within her research, she focuses on digital justice and the position of minors as consumers, particularly in relation to microtransactions, gaming ecosystems, and monetisation models that may affect transparency, autonomy, and fairness in digital consumer relations. Her work seeks to contribute to a better understanding of how private law and consumer protection can respond to emerging challenges in digital markets.</t>
+  </si>
+  <si>
+    <t>Michala_Špačková.jpg</t>
+  </si>
+  <si>
+    <t>Dana_Ondrejová.jpg</t>
   </si>
 </sst>
 </file>
@@ -2391,6 +2403,12 @@
       <c r="F45" t="s">
         <v>169</v>
       </c>
+      <c r="G45" t="s">
+        <v>286</v>
+      </c>
+      <c r="I45" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
@@ -2450,6 +2468,12 @@
       </c>
       <c r="F48" t="s">
         <v>169</v>
+      </c>
+      <c r="G48" t="s">
+        <v>287</v>
+      </c>
+      <c r="I48" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:9">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E6F281-CE47-4CBE-8E30-3FD1B12277EF}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECAB50A4-3AB8-4DB0-8FC8-966AD40933F6}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="292">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -986,6 +986,12 @@
   </si>
   <si>
     <t>Dana_Ondrejová.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Václav Brož is a lecturer and researcher in economics and finance at the Charles University in Prague. He has policy experience with the Czech National Bank and his research interests are regulatory &amp; enforcement actions, banking, and inflation.</t>
+  </si>
+  <si>
+    <t>vaclav_broz.jpg</t>
   </si>
 </sst>
 </file>
@@ -2609,6 +2615,12 @@
       <c r="F56" t="s">
         <v>169</v>
       </c>
+      <c r="G56" t="s">
+        <v>290</v>
+      </c>
+      <c r="I56" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECAB50A4-3AB8-4DB0-8FC8-966AD40933F6}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F47817-EA7D-4511-8879-29F57896B051}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="298">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -992,6 +992,24 @@
   </si>
   <si>
     <t>vaclav_broz.jpg</t>
+  </si>
+  <si>
+    <t>will.bennis@vse.cz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathalie Müller </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müller </t>
+  </si>
+  <si>
+    <t>nathalie.muller@vse.cz</t>
+  </si>
+  <si>
+    <t>Nathalie’s research focuses on behavioral and experimental economics, with a particular interest in social norms, peer effects, and health behaviors. She studies how social incentives and expectations influence individual decision-making, and how moralization, identity, and polarization shape behavior in collective and environmental contexts. Combining theoretical insights from economics with experimental methods, her work examines the mechanisms through which social influences drive human behavior across health and societal domains.</t>
+  </si>
+  <si>
+    <t>Nathalie_Muller.jpg</t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE358DA8-D777-4377-96EA-27F7BC555635}">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -2931,6 +2949,9 @@
       <c r="C71" t="s">
         <v>129</v>
       </c>
+      <c r="D71" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="E71" t="s">
         <v>198</v>
       </c>
@@ -3153,6 +3174,32 @@
       </c>
       <c r="I79" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>293</v>
+      </c>
+      <c r="B80" t="s">
+        <v>294</v>
+      </c>
+      <c r="C80" t="s">
+        <v>129</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E80" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" t="s">
+        <v>169</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="I80" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -3170,8 +3217,10 @@
     <hyperlink ref="D64" r:id="rId11" tooltip="mailto:laurent.weill@unistra.fr" display="mailto:laurent.weill@unistra.fr" xr:uid="{C04E6286-39F3-41C0-84AF-3F9E019F1780}"/>
     <hyperlink ref="H64" r:id="rId12" tooltip="https://sites.google.com/site/laurentweillstrasbourg/home" xr:uid="{C03A4B72-D83E-424B-A875-03CA43C73FAB}"/>
     <hyperlink ref="H4" r:id="rId13" tooltip="https://annairenebaka.com/" xr:uid="{CD375092-C532-49C6-AC57-E1CCBA77229B}"/>
+    <hyperlink ref="D71" r:id="rId14" xr:uid="{793FC673-BD08-49A5-B2EB-0A2BE0E61BE6}"/>
+    <hyperlink ref="D80" r:id="rId15" xr:uid="{09431866-B94B-4267-880A-C72486C77788}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId16"/>
 </worksheet>
 </file>
--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F47817-EA7D-4511-8879-29F57896B051}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789004C3-FAEF-42EE-A128-C083EDD3ADC8}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="300">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1010,6 +1010,12 @@
   </si>
   <si>
     <t>Nathalie_Muller.jpg</t>
+  </si>
+  <si>
+    <t>Zuzana Ambrozková is a PhD candidate at the Department of Political Science and Sociology at Faculty of Law, Charles University. Her research focuses on the intersection of emotions and law, particulary on offenders’ remorse and its role in criminal law, and on the role of judges’ emotions in judicial decision-making and management of court proceedings. </t>
+  </si>
+  <si>
+    <t>zuzana_ambrozkova.jpg</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1496,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="15.6">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -1508,6 +1514,12 @@
       </c>
       <c r="F2" t="s">
         <v>169</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:9">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789004C3-FAEF-42EE-A128-C083EDD3ADC8}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE9423F-A8F9-450B-B88B-63E819571373}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="304">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1016,6 +1016,18 @@
   </si>
   <si>
     <t>zuzana_ambrozkova.jpg</t>
+  </si>
+  <si>
+    <t>Pavel Loutocký is assistant professor and post-doctorate researcher at the Institute of Law and Technology, Faculty of Law, Masaryk University and Faculty of Informatics, Masaryk University. He participated in a number of national and international research and delivered lectures concerning online dispute resolution, electronic identification and documents, online consumer protection, cybersecurity or online platforms. Since 2012, he has been a regular observer of selected working groups within the United Nations Commission on International Trade Law (UNCITRAL). He is also an external lecturer at the Georg-August-Universität Göttingen, Danube University Krems or University of Pécs and became a fellow of the National Center for Technology &amp; Dispute Resolution in US. He is also a fellow at Information Society Law Center at University of Milan and listed as an expert by ENISA.</t>
+  </si>
+  <si>
+    <t>Pavel_Loutocky.jpg</t>
+  </si>
+  <si>
+    <t>Anezka_Karpjakova.jpeg</t>
+  </si>
+  <si>
+    <t>Mgr. Bc. Anežka Karpjáková is a doctoral researcher at the Institute of Law and Technology, Faculty of Law, Masaryk University, where she is also enrolled in the Ph.D. programme in Law of Information and Communication Technologies. Her doctoral research focuses on legal measures for the prevention of and protection of bank clients against online payment fraud based on social engineering methods.</t>
   </si>
 </sst>
 </file>
@@ -2465,6 +2477,12 @@
       <c r="F46" t="s">
         <v>169</v>
       </c>
+      <c r="G46" t="s">
+        <v>303</v>
+      </c>
+      <c r="I46" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
@@ -2570,6 +2588,12 @@
       </c>
       <c r="F51" t="s">
         <v>169</v>
+      </c>
+      <c r="G51" t="s">
+        <v>300</v>
+      </c>
+      <c r="I51" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:9">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE9423F-A8F9-450B-B88B-63E819571373}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B877C3E-C0D8-4BB6-A79D-0B7663A05EF2}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="308">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1028,6 +1028,18 @@
   </si>
   <si>
     <t>Mgr. Bc. Anežka Karpjáková is a doctoral researcher at the Institute of Law and Technology, Faculty of Law, Masaryk University, where she is also enrolled in the Ph.D. programme in Law of Information and Communication Technologies. Her doctoral research focuses on legal measures for the prevention of and protection of bank clients against online payment fraud based on social engineering methods.</t>
+  </si>
+  <si>
+    <t>Jaromír Baxa is an Assistant Professor at the Charles University, Faculty of Social Sciences. His research interests are mainly related to monetary policy, inflation dynamics and economic effects of uncertainty.</t>
+  </si>
+  <si>
+    <t>jaromir_baxa.jpg</t>
+  </si>
+  <si>
+    <t>Štěpán Šanda is a PhD candidate and academic researcher at the Prague University of Economics and Business (VŠE). He is involved in multiple research projects in the field of energy, focusing primarily on demand-side flexibility, energy literacy, and the behavioral aspects of household energy consumption in the context of the energy transition.</t>
+  </si>
+  <si>
+    <t>stepan_sanda.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2894,6 +2906,12 @@
       <c r="F65" t="s">
         <v>169</v>
       </c>
+      <c r="G65" t="s">
+        <v>304</v>
+      </c>
+      <c r="I65" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
@@ -3071,6 +3089,12 @@
       </c>
       <c r="F74" t="s">
         <v>169</v>
+      </c>
+      <c r="G74" t="s">
+        <v>306</v>
+      </c>
+      <c r="I74" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="75" spans="1:9">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B877C3E-C0D8-4BB6-A79D-0B7663A05EF2}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB6C709D-B8A7-4C38-BA29-D94BC379789C}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-27405" yWindow="-2685" windowWidth="21600" windowHeight="11235" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="310">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1040,6 +1040,12 @@
   </si>
   <si>
     <t>stepan_sanda.jpeg</t>
+  </si>
+  <si>
+    <t>Aycan Funda is a PhD student in Theoretical Legal Sciences at Charles University and a researcher at the Institute for the Interregional Study of Constitutionalism. Her work in the philosophy of law explores the normative foundations of constitutional belonging. Drawing on recognition theory, she examines how constitutionalism and authenticity are deeply connected through the processes of collective identity formation. Her research is informed by her earlier studies in ethics and political philosophy, which include a Research Master from KU Leuven and an M.A. from Erasmus University Rotterdam.</t>
+  </si>
+  <si>
+    <t>Aycan Funda.jpg</t>
   </si>
 </sst>
 </file>
@@ -1818,6 +1824,12 @@
       <c r="F14" t="s">
         <v>169</v>
       </c>
+      <c r="G14" t="s">
+        <v>308</v>
+      </c>
+      <c r="I14" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB6C709D-B8A7-4C38-BA29-D94BC379789C}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D1F570E-2B7A-4953-8A50-1503E190DCD3}"/>
   <bookViews>
-    <workbookView xWindow="-27405" yWindow="-2685" windowWidth="21600" windowHeight="11235" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="315">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1047,12 +1047,27 @@
   <si>
     <t>Aycan Funda.jpg</t>
   </si>
+  <si>
+    <t>Zuzana Chytková</t>
+  </si>
+  <si>
+    <t>Chytková</t>
+  </si>
+  <si>
+    <t>Zuzana Chytková is Associate Professor at Faculty of Business Administration, Prague University of Economics and Business. Her research focuses on qualitative approaches to consumer behaviour, with a long-term interest in market inequalities and disadvantaged market actors. </t>
+  </si>
+  <si>
+    <t>Zuzana_Chytkova.jpg</t>
+  </si>
+  <si>
+    <t>zuzana.chytkova@vse.cz</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1121,6 +1136,14 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1144,7 +1167,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1155,6 +1178,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1491,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE358DA8-D777-4377-96EA-27F7BC555635}">
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -3272,6 +3296,32 @@
       </c>
       <c r="I80" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>310</v>
+      </c>
+      <c r="B81" t="s">
+        <v>311</v>
+      </c>
+      <c r="C81" t="s">
+        <v>129</v>
+      </c>
+      <c r="D81" t="s">
+        <v>314</v>
+      </c>
+      <c r="E81" t="s">
+        <v>198</v>
+      </c>
+      <c r="F81" t="s">
+        <v>169</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="I81" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D1F570E-2B7A-4953-8A50-1503E190DCD3}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2068BFF3-19F7-4A44-9358-A6D671001C4E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="319">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1061,6 +1061,18 @@
   </si>
   <si>
     <t>zuzana.chytkova@vse.cz</t>
+  </si>
+  <si>
+    <t>Jakub_Harasta.jpg</t>
+  </si>
+  <si>
+    <t>Josef_Kotasek.jpg</t>
+  </si>
+  <si>
+    <t>Jakub Harasta is an Associate Professor at the Institute of Law and Technology. His research focuses on legal issues of cybersecurity and data protection, as well as on artificial intelligence and human-computer interaction within the legal domain. Jakub has participated in and led several national and international projects in these areas. He explores how technologies shape legal decision-making, the regulatory framework, and the protection of fundamental rights.</t>
+  </si>
+  <si>
+    <t>Prof. JUDr. Josef Kotásek, Ph.D., serves as the Head of the Department of Commercial Law at the Faculty of Law, Masaryk University in Brno. His scholarly focus lies primarily in commercial law, securities law, unfair competition, and consumer protection. In recent years, he has concentrated on the legal regulation of advertising, including issues of sexist advertising, self-regulation, gender aspects of marketing communication, and unfair commercial practices in the digital environment. In his academic work, he connects traditional topics of commercial and competition law with current issues of European regulation, consumer vulnerability, online platforms, and transformations of the market driven by digitalisation.</t>
   </si>
 </sst>
 </file>
@@ -2419,6 +2431,12 @@
       <c r="F41" t="s">
         <v>169</v>
       </c>
+      <c r="G41" t="s">
+        <v>317</v>
+      </c>
+      <c r="I41" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
@@ -2478,6 +2496,12 @@
       </c>
       <c r="F44" t="s">
         <v>169</v>
+      </c>
+      <c r="G44" t="s">
+        <v>318</v>
+      </c>
+      <c r="I44" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:9">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2068BFF3-19F7-4A44-9358-A6D671001C4E}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F212611D-1003-4B13-8D28-0CBAF01D597C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
+    <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
   <sheets>
     <sheet name="PF UK" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="321">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1073,6 +1073,12 @@
   </si>
   <si>
     <t>Prof. JUDr. Josef Kotásek, Ph.D., serves as the Head of the Department of Commercial Law at the Faculty of Law, Masaryk University in Brno. His scholarly focus lies primarily in commercial law, securities law, unfair competition, and consumer protection. In recent years, he has concentrated on the legal regulation of advertising, including issues of sexist advertising, self-regulation, gender aspects of marketing communication, and unfair commercial practices in the digital environment. In his academic work, he connects traditional topics of commercial and competition law with current issues of European regulation, consumer vulnerability, online platforms, and transformations of the market driven by digitalisation.</t>
+  </si>
+  <si>
+    <t>KlaraKantova.png</t>
+  </si>
+  <si>
+    <t>Klára Kantová is a PhD candidate in Economics and Finance at the Institute of Economic Studies, Charles University, focusing on labor, behavioral, and experimental economics, meta-analysis, and discrimination studies. She also serves as a researcher and head of the Center for Doctoral Studies at IES, Charles University.</t>
   </si>
 </sst>
 </file>
@@ -2012,6 +2018,12 @@
       <c r="F21" t="s">
         <v>169</v>
       </c>
+      <c r="G21" t="s">
+        <v>320</v>
+      </c>
+      <c r="I21" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F212611D-1003-4B13-8D28-0CBAF01D597C}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51ED7243-9DB7-4C22-A126-A9AACA4EB605}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="326">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1079,6 +1079,21 @@
   </si>
   <si>
     <t>Klára Kantová is a PhD candidate in Economics and Finance at the Institute of Economic Studies, Charles University, focusing on labor, behavioral, and experimental economics, meta-analysis, and discrimination studies. She also serves as a researcher and head of the Center for Doctoral Studies at IES, Charles University.</t>
+  </si>
+  <si>
+    <t>Edin Hodzic_photo.jpg</t>
+  </si>
+  <si>
+    <t>Edin Hodžić is a Research Fellow at the Faculty of Law, Charles University. His academic work spans international human rights law, comparative law, and law and public policy. He brings two decades of field experience in rule of law and human rights programming, particularly in the Western Balkans, and has advised international organizations—including UN, the Council of Europe, and the OSCE—on legal and policy matters. He has published on human rights and rule of law across topics including anti-discrimination, political participation, and transitional justice. His current research focuses on the protection of human rights in the context of new technologies. He holds a PhD from the Faculty of Law, McGill University.</t>
+  </si>
+  <si>
+    <t>https://josefmontag.github.io/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Josef Montag holds a PhD in Law and Economics from the University of Turin. His research is mostly empirical, often using experimental methods. He deals with questions pertaining to criminal behavior, judicial heterogeneity, gender gap, ethnic discrimination, housing, and unemployment. He serves as an Associate Professor at the Department of Economics, Faculty of Law, Charles University and is the Principal Investigator of the Center for Inequality and Open Society. </t>
+  </si>
+  <si>
+    <t>Josef_Montag.jpg</t>
   </si>
 </sst>
 </file>
@@ -1932,6 +1947,12 @@
       <c r="F17" t="s">
         <v>169</v>
       </c>
+      <c r="G17" t="s">
+        <v>322</v>
+      </c>
+      <c r="I17" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
@@ -2213,6 +2234,15 @@
       </c>
       <c r="F29" t="s">
         <v>169</v>
+      </c>
+      <c r="G29" t="s">
+        <v>324</v>
+      </c>
+      <c r="H29" t="s">
+        <v>323</v>
+      </c>
+      <c r="I29" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="30" spans="1:9">

--- a/public/team.xlsx
+++ b/public/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cunicz-my.sharepoint.com/personal/47213138_cuni_cz/Documents/Plocha/Web CIOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51ED7243-9DB7-4C22-A126-A9AACA4EB605}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{82039D76-65C3-4C60-B52B-D0714FBC821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB710437-FEE7-4DAD-8FF6-72E35298A51F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4200" windowWidth="29040" windowHeight="15720" xr2:uid="{36CEB803-AFCD-4782-815A-CCF861C6B502}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="332">
   <si>
     <t>Ambrozková</t>
   </si>
@@ -1095,12 +1095,41 @@
   <si>
     <t>Josef_Montag.jpg</t>
   </si>
+  <si>
+    <r>
+      <t>Jakub Drápal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t> is an Associate Professor at the Charles University Faculty of Law and a researcher at the Institute of State and Law of the Czech Academy of Sciences. His research lies at the intersection of criminal law, criminology, and empirical legal studies, with a particular focus on sentencing, judicial decision-making, prisons, and penal policy. He combines doctrinal legal analysis with quantitative and computational methods to examine how courts make sentencing decisions and how punishment is administered in practice. He currently leads an ERC Starting Grant project on sentencing and judicial discretion in Europe and has published extensively on criminal justice, punishment, and empirical approaches to law.</t>
+    </r>
+  </si>
+  <si>
+    <t>jakub_drapal.jpg</t>
+  </si>
+  <si>
+    <t>buryskova.cz/en</t>
+  </si>
+  <si>
+    <t>Tereza Burýšková (maiden name Hofrichterová) is a Ph.D. candidate in Economics at CERGE-EI, with an interdisciplinary background in law, mathematics, and physics from Charles University. Her research focuses on behavioral, information, and attention economics, as well as law and economics. Her current work explores topics such as media influence, platform design, and judicial decision-making.  </t>
+  </si>
+  <si>
+    <t>tereza_buryskova.png</t>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/jakub-drapal</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1177,6 +1206,13 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1200,7 +1236,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1212,6 +1248,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1746,6 +1783,15 @@
       <c r="F8" t="s">
         <v>169</v>
       </c>
+      <c r="G8" t="s">
+        <v>329</v>
+      </c>
+      <c r="H8" t="s">
+        <v>328</v>
+      </c>
+      <c r="I8" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="13.2" customHeight="1">
       <c r="A9" t="s">
@@ -1791,6 +1837,15 @@
       </c>
       <c r="F10" t="s">
         <v>169</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I10" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3407,8 +3462,9 @@
     <hyperlink ref="H4" r:id="rId13" tooltip="https://annairenebaka.com/" xr:uid="{CD375092-C532-49C6-AC57-E1CCBA77229B}"/>
     <hyperlink ref="D71" r:id="rId14" xr:uid="{793FC673-BD08-49A5-B2EB-0A2BE0E61BE6}"/>
     <hyperlink ref="D80" r:id="rId15" xr:uid="{09431866-B94B-4267-880A-C72486C77788}"/>
+    <hyperlink ref="H10" r:id="rId16" tooltip="https://sites.google.com/view/jakub-drapal" xr:uid="{77007AD5-735A-4ABC-A930-5745BAE05435}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId16"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId17"/>
 </worksheet>
 </file>